--- a/templates/XLSX-Muster.xlsx
+++ b/templates/XLSX-Muster.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m3-jo\OneDrive\Dokumente\Schlauchmanegtment App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{31B320F1-DEAF-436B-9AFF-9D4ADA9EB3E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0322A300-4BC1-43AA-8AC7-0105688276A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookPassword="C43E" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1D6CE806-F6E4-4A9C-944A-DA6664F354E5}"/>
+    <workbookView xWindow="1380" yWindow="0" windowWidth="24450" windowHeight="12690" xr2:uid="{FE28AD4D-3E1E-44CE-A0E8-8039B372313B}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -21,19 +21,19 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$Q$30</definedName>
     <definedName name="Anschlüsse">Auswahlseite!$C:$C</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Tabelle1!$A$1:$Y$1050</definedName>
+    <definedName name="Nennweite10">Tabelle1!$W$2:$W$97</definedName>
+    <definedName name="Nennweite12">Tabelle1!$X$2:$X$97</definedName>
+    <definedName name="Nennweite16">Tabelle1!$Y$2:$Y$97</definedName>
+    <definedName name="Nennweite18">Tabelle1!$Z$2:$Z$97</definedName>
+    <definedName name="Nennweite20">Tabelle1!$AA$2:$AA$97</definedName>
+    <definedName name="Nennweite25">Tabelle1!$AB$2:$AB$98</definedName>
+    <definedName name="Nennweite32">Tabelle1!$AC$2:$AC$97</definedName>
+    <definedName name="Nennweite40">Tabelle1!$AD$2:$AD$97</definedName>
+    <definedName name="Nennweite50">Tabelle1!$AE$2:$AE$97</definedName>
+    <definedName name="Nennweite6">Tabelle1!$U$2:$U$97</definedName>
+    <definedName name="Nennweite60">Tabelle1!$AF$2:$AF$97</definedName>
+    <definedName name="Nennweite8">Tabelle1!$V$2:$V$97</definedName>
     <definedName name="NW">Auswahlseite!$B:$B</definedName>
-    <definedName name="_NW10">Tabelle1!$W$2:$W$97</definedName>
-    <definedName name="_NW12">Tabelle1!$X$2:$X$97</definedName>
-    <definedName name="_NW16">Tabelle1!$Y$2:$Y$97</definedName>
-    <definedName name="_NW18">Tabelle1!$Z$2:$Z$97</definedName>
-    <definedName name="_NW20">Tabelle1!$AA$2:$AA$97</definedName>
-    <definedName name="_NW25">Tabelle1!$AB$2:$AB$98</definedName>
-    <definedName name="_NW32">Tabelle1!$AC$2:$AC$97</definedName>
-    <definedName name="_NW40">Tabelle1!$AD$2:$AD$97</definedName>
-    <definedName name="_NW50">Tabelle1!$AE$2:$AE$97</definedName>
-    <definedName name="_NW6">Tabelle1!$U$2:$U$97</definedName>
-    <definedName name="_NW60">Tabelle1!$AF$2:$AF$97</definedName>
-    <definedName name="_NW8">Tabelle1!$V$2:$V$97</definedName>
     <definedName name="Schlauch">Auswahlseite!$A$1:$A$14</definedName>
     <definedName name="Z_D2AFBCA2_9A24_4255_A9B7_2295FB37AFD5_.wvu.FilterData" localSheetId="0" hidden="1">Tabelle1!$A$1:$Q$30</definedName>
   </definedNames>
@@ -3205,7 +3205,7 @@
         <xdr:cNvPr id="4324" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D490BC2-82A4-FBDC-4859-5479FCE2CF42}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83769249-4D88-8081-6BBB-5C8C356086C2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3279,7 +3279,7 @@
         <xdr:cNvPr id="4325" name="Grafik 39">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA9BBF23-0A1E-5FBF-9021-37CE442C2735}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{063D910F-1B43-778C-95EC-47E78A66457F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3353,7 +3353,7 @@
         <xdr:cNvPr id="4326" name="Grafik 40">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EB13C69-45C8-F447-8EAF-98FBB16F1C06}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3703DA63-FD76-DAB4-B642-C4361DD4F411}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3427,7 +3427,7 @@
         <xdr:cNvPr id="4327" name="Grafik 41">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{763A8A78-F9F1-BF85-ED77-B645D8F739F6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F674678-B34F-E49F-289A-C3742E8FDACD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3501,7 +3501,7 @@
         <xdr:cNvPr id="4328" name="Grafik 42">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92AB1A00-8DBA-0E35-ADC9-889C80F1372A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{727AEBD0-FCE1-E0F1-1CFD-8F4C2DFD9A57}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3575,7 +3575,7 @@
         <xdr:cNvPr id="4329" name="Grafik 43">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55F7694A-C337-D8A3-C33F-B281A982BA4F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9356409-C730-B360-6EAA-014BD52F9D49}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3649,7 +3649,7 @@
         <xdr:cNvPr id="4330" name="Grafik 44">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD6BD41A-9D36-DEF6-E033-526E2BA4E66C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40E8A53F-525E-498B-107B-9BF94B2D3391}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3723,7 +3723,7 @@
         <xdr:cNvPr id="4331" name="Grafik 45">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68EB754E-3093-28F5-4E6F-28B9F86E720E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF56E592-7A15-7A69-6A66-6153E5D18CC3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3797,7 +3797,7 @@
         <xdr:cNvPr id="4332" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5B823ED-8C49-6FA4-AA68-964BBE95D6CE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE998EC5-4146-8C2F-8DD1-0C54B053BDF9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3871,7 +3871,7 @@
         <xdr:cNvPr id="4333" name="Grafik 48">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91F76F3C-C8CD-52CE-F4E8-C061D56F0EF7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4AE643D-412F-512F-3967-2D5BBFAE8C24}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3945,7 +3945,7 @@
         <xdr:cNvPr id="4334" name="Grafik 49">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{176F885E-6C93-9B6E-A415-33C104563FB1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93004270-6F96-628A-3A78-E64BBF8E9D11}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4019,7 +4019,7 @@
         <xdr:cNvPr id="4335" name="Grafik 51">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{932F2862-DA08-5100-DB43-BAD517F1F535}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B939C023-D1EE-EDE6-6031-50BDDC25BDC2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4093,7 +4093,7 @@
         <xdr:cNvPr id="4336" name="Grafik 52">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6556E8F8-30A4-C8C0-B033-9A5276C7307F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5594067A-6DDF-0FEF-48AE-492FB296C1A2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4167,7 +4167,7 @@
         <xdr:cNvPr id="4337" name="Grafik 53">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEE9A984-4F88-9D24-2B5C-CE8FF355C535}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4DD90FB-269E-636C-10B4-D7CA22A52247}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4241,7 +4241,7 @@
         <xdr:cNvPr id="4338" name="Grafik 54">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34450AB0-BD9A-8954-0208-E4A3E9A12AC2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BA92EA8-7407-F83C-44FD-AD03AD475134}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4315,7 +4315,7 @@
         <xdr:cNvPr id="4339" name="Grafik 56">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3200827E-D2A4-8A11-B222-785A079EFC01}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77766B57-9059-3E4F-5891-4A7F9BA80986}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4389,7 +4389,7 @@
         <xdr:cNvPr id="4340" name="Grafik 57">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B2D2D46-9569-57CD-B93D-080423A5F5B4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{539DFED3-300E-67FD-4EE2-6FDF7C00B88E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4463,7 +4463,7 @@
         <xdr:cNvPr id="4341" name="Grafik 39">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8140C0DE-6546-D9E3-1C88-261E4B9904DE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93FD8FB0-59AB-847F-5B02-0EEF3ABACE6F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4537,7 +4537,7 @@
         <xdr:cNvPr id="4342" name="Grafik 40">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8448B07-0298-0BF2-07DF-836F52213FD1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7D6C5CF-7849-85A6-4DF6-8C2056A27A4A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4611,7 +4611,7 @@
         <xdr:cNvPr id="4343" name="Grafik 41">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{029D4D93-7539-1A98-6190-B60DDCE4BCE3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35C7928C-CCD7-8457-42C2-1A859D70554A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4685,7 +4685,7 @@
         <xdr:cNvPr id="4344" name="Grafik 42">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E794E01-683B-31CE-ABA6-0879B6C09DD9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{897B725E-2A20-E2CE-8981-605DE684E8EF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4759,7 +4759,7 @@
         <xdr:cNvPr id="4345" name="Grafik 43">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D8483E0-432F-051D-A52C-2AD69F9277DE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{767C53E8-281F-4463-04F9-38CBBE72B62C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4833,7 +4833,7 @@
         <xdr:cNvPr id="4346" name="Grafik 44">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B52DB527-B148-2D4F-289B-DB13B92F238B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F55D0F68-9DFA-48F5-BEAD-8D9D4A2BD1BC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4907,7 +4907,7 @@
         <xdr:cNvPr id="4347" name="Grafik 45">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C9FC23B-5D07-EE29-98D3-63A27BD28D72}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4A60528-B88C-7329-6623-C1A975A3E6D5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4981,7 +4981,7 @@
         <xdr:cNvPr id="4348" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E57F6CB-93D1-1054-817A-6F8A1150099A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48AABAB4-CCED-6672-6AA2-BD18D31D7A91}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5055,7 +5055,7 @@
         <xdr:cNvPr id="4349" name="Grafik 48">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4F10F9A-2310-4A15-DDD5-470B9018BF55}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D27F7C34-D38C-D553-CFD8-8CBE0EBFDD38}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5129,7 +5129,7 @@
         <xdr:cNvPr id="4350" name="Grafik 49">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{793C8785-15F1-3422-8DE1-8914E8C0E3C0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20245118-09FB-ECF3-5508-2AB9786251D1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5203,7 +5203,7 @@
         <xdr:cNvPr id="4351" name="Grafik 51">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA7643FC-E922-B4DC-C9E9-67CF1EA48B8F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B270F4F-F74A-50A5-B85A-3348B303C85F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5277,7 +5277,7 @@
         <xdr:cNvPr id="4352" name="Grafik 52">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7B66226-A6B1-2DF9-3E71-4E24E39F84E1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD8857DB-7F8F-9D65-0FA5-C3F48052EA51}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5351,7 +5351,7 @@
         <xdr:cNvPr id="4353" name="Grafik 53">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F501454-4909-0489-2EF1-538EE7EB3D8A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D56D271-EF13-F540-DCA8-B60C98890101}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5425,7 +5425,7 @@
         <xdr:cNvPr id="4354" name="Grafik 54">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41B6B26B-62CD-4460-E659-7E6D8B249DF3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F82711C-A454-46C7-4FC5-C558FC45F8BC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5499,7 +5499,7 @@
         <xdr:cNvPr id="4355" name="Grafik 56">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9EF51EC-95FF-9F30-33E5-A366709CC2F7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F32D8A45-2048-EFDE-870E-564765A52E4F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5573,7 +5573,7 @@
         <xdr:cNvPr id="4356" name="Grafik 57">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BFCBB7B-F99E-6C25-E1AE-7BA28B22BEB7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49A449BA-AE94-6F8A-ED12-69E234047C44}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5647,7 +5647,7 @@
         <xdr:cNvPr id="4357" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{323614C2-8E56-6DDE-987E-3465BDF85182}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EDC2178-43FB-F9C6-CDAD-DEDD179410C6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5721,7 +5721,7 @@
         <xdr:cNvPr id="4358" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{248DE0F8-9113-928D-7DA0-A9CB91D0A7E5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D17433B7-836E-B18C-3991-C17D2C2091E3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5795,7 +5795,7 @@
         <xdr:cNvPr id="4359" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B78BF29D-D145-04B8-5A00-4A424B957383}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79465E90-4728-1244-F4DB-63EC6AB81932}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5869,7 +5869,7 @@
         <xdr:cNvPr id="4360" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1714C302-D074-0736-A04B-5D0DE51E57DA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7C383BC-9662-8B04-66C2-13831AFF7028}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5943,7 +5943,7 @@
         <xdr:cNvPr id="4361" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E23BFBFC-A074-9B2F-7DBF-2B54AA3BEED0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AFF3213-4A6B-00B2-1727-14F7B4FA2E22}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6017,7 +6017,7 @@
         <xdr:cNvPr id="4362" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4255D2F-C023-B868-2836-A5B2501A8173}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D077C85A-93FB-6F19-7CAB-E75199AF3C6E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6091,7 +6091,7 @@
         <xdr:cNvPr id="4363" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{410A7924-0E05-B79B-90A6-4C3F7809BF80}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3607D15-2A94-E89D-9C7F-146AAAFC7DF2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6165,7 +6165,7 @@
         <xdr:cNvPr id="4364" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A4611C3-CB9A-1024-D507-507BDD6B49F6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0E0B0FA-6DBD-47B7-43EF-3CD30C4D7DB5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6239,7 +6239,7 @@
         <xdr:cNvPr id="4365" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C24BA261-80C0-70AB-DC3A-37955658D796}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C23528A-8F96-EED7-EEC2-8A3AA471B9FC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6313,7 +6313,7 @@
         <xdr:cNvPr id="4366" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA7CB351-211C-B2EE-F0C1-0AF20BD45C75}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A40C18E1-CEAD-BE88-1261-FD549F28E158}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6387,7 +6387,7 @@
         <xdr:cNvPr id="4367" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1685AE5-B861-1D34-F0F9-68E876DB7D34}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29EAFB07-59DD-B2B9-5121-3850AB5BB58E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6461,7 +6461,7 @@
         <xdr:cNvPr id="4368" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB3AD252-884F-CFD9-80F8-45AA176F0968}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC1053F1-0281-977A-92A6-108134BB0B1A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6535,7 +6535,7 @@
         <xdr:cNvPr id="4369" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F289D5B-A858-FA73-5325-11BAFC4053CF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC5A2A14-675D-32E2-EA14-163421BA6188}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6609,7 +6609,7 @@
         <xdr:cNvPr id="4370" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{158BEA87-CDEB-B0A9-CDA5-3C9F06976411}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5303196-3BF3-AA75-CEFE-401893B9D72E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6683,7 +6683,7 @@
         <xdr:cNvPr id="4371" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A5A73D8-F7F0-5486-3BF0-4E38355B7C81}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69B4A8BB-3F09-223D-5528-AEDFEAEC5F35}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6757,7 +6757,7 @@
         <xdr:cNvPr id="4372" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19C84689-1356-0EEC-FD63-E96C867F9318}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BF2FBE5-14BF-AC2E-9ED6-C03431D735C1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6831,7 +6831,7 @@
         <xdr:cNvPr id="4373" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22AE13C9-736D-8B90-B9F3-D271692CBCDF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{830B9D54-0EED-EE1D-486E-BC1F55F4E874}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6905,7 +6905,7 @@
         <xdr:cNvPr id="4374" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B840CFD1-7BBD-E10B-B8D0-6352D4B711C3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5B2B8BA-89D4-FB42-D010-77B5AB751A3D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6979,7 +6979,7 @@
         <xdr:cNvPr id="4375" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E58F018F-1924-1633-6886-3AE9B1476DC8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E25CC927-D215-271D-F884-5E64B3322DB2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7053,7 +7053,7 @@
         <xdr:cNvPr id="4376" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7998F03E-EBDD-9036-DEF4-97A7247C6870}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4A3C1E7-68B0-011D-747C-A6E62978430E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7127,7 +7127,7 @@
         <xdr:cNvPr id="4377" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66C7A662-31FE-711A-FC49-F231AE606A03}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{771EEB6A-0782-0CAF-FB58-E218F64CA7FC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7201,7 +7201,7 @@
         <xdr:cNvPr id="4378" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{349A0EAA-0EE0-5228-91C8-682736AC769C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC44C50E-BC14-FD3E-69E6-3C0CC4F5D948}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7275,7 +7275,7 @@
         <xdr:cNvPr id="4379" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B187DDA-51A9-4F3F-7744-EBE2C5610505}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D756BD3A-78FA-2E79-643C-CDE7B7565781}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7349,7 +7349,7 @@
         <xdr:cNvPr id="4380" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20E7018E-8DAC-FA94-74CB-81CD4E77DEED}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DEF27B6-B63F-B2D8-4DD0-0AA241DB512F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7423,7 +7423,7 @@
         <xdr:cNvPr id="4381" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C85A1936-4E86-04A1-88AC-0E1440F0EE5F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3EFF195-9EB9-DA20-81D9-B2D5641CAF9B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7497,7 +7497,7 @@
         <xdr:cNvPr id="4382" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{188FCB14-BEBC-E8CD-2F6D-A1845641BB58}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24CCD815-11E8-2E95-AE56-EDAA95687CAC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7571,7 +7571,7 @@
         <xdr:cNvPr id="4383" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E58A1D1-51D6-19A9-FF05-37FC4FB51EB9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C3B12DF-EBF9-B684-9CA1-E6402EFBCD6E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7645,7 +7645,7 @@
         <xdr:cNvPr id="4384" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D038F06-DBDD-5A69-5A68-B2DAD682A116}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3870DBB-7F28-E9D7-F1DD-1B2C2B680821}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7719,7 +7719,7 @@
         <xdr:cNvPr id="4385" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32EFC009-A79B-5C3E-B84E-72FC3BA227B1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B591F8A1-8ED8-3E0A-F8AF-E4B4C9B49134}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7793,7 +7793,7 @@
         <xdr:cNvPr id="4386" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{623CBE2A-6D00-A454-9859-C86577665DD5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DBD2491-9346-93F8-E0D4-76B5B4C59D64}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7867,7 +7867,7 @@
         <xdr:cNvPr id="4387" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB4318A2-3C49-69BD-517F-CA279E9AE37B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0FE21A2-1AFD-4E87-576B-53D963E092C6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7941,7 +7941,7 @@
         <xdr:cNvPr id="4388" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F79088B7-3522-AA5B-FFDA-2AEFC3567679}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D84F67F4-DBCD-798E-FF62-E53CB98BAA3A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8015,7 +8015,7 @@
         <xdr:cNvPr id="4389" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{681AB2A7-DF12-136A-5FB8-07CF64EA7BDD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77EA2D5E-EB6C-182F-444A-A61589E2A7A2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8089,7 +8089,7 @@
         <xdr:cNvPr id="4390" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5037D828-DA3A-F048-FBCA-AD6278EA9A6B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EEC0783-7261-4951-8728-B0BF68D3078F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8163,7 +8163,7 @@
         <xdr:cNvPr id="4391" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A45FDC5C-5B1C-30D7-AE67-E4DD6A3C065B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000546-1DBD-9148-248C-9B06F15AA450}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8237,7 +8237,7 @@
         <xdr:cNvPr id="4392" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13BB404B-C01D-D560-9109-23A917549CAA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BFA4FFE-6D81-14D4-446E-50F51F624939}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8311,7 +8311,7 @@
         <xdr:cNvPr id="4393" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2956F761-BE4A-E914-6FFD-C828763B73AD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9C0954C-5DDC-9DB6-7143-D572FFC53F86}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8385,7 +8385,7 @@
         <xdr:cNvPr id="4394" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D96E1061-C96E-24B3-B7AB-45ECE0CF04DA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23B7F9B6-3473-B305-E9A0-01D675A997CB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8459,7 +8459,7 @@
         <xdr:cNvPr id="4395" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85071875-130D-2FD5-87C9-7F82EB648711}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBF4AF72-43F1-0B20-FB79-54859803B1A2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8533,7 +8533,7 @@
         <xdr:cNvPr id="4396" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39ACBD34-9620-A4DE-71FE-165AB0BFBB37}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33D52368-6FDC-938E-1859-CF8493EEEAE8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8607,7 +8607,7 @@
         <xdr:cNvPr id="4397" name="Grafik 56">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2606A146-8FA6-55DB-4C39-BC89AE868ABE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F5F3BC9-CB04-CD6A-E041-F601EDACF3FB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8681,7 +8681,7 @@
         <xdr:cNvPr id="4398" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7B34EE8-8BE7-74CD-1108-07D46B8AA256}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5BC65FA-5C02-5B21-FD82-0F16B7B7F8C6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8755,7 +8755,7 @@
         <xdr:cNvPr id="4399" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F923994-0EDD-B6DF-9278-48489A16AB27}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA7696A0-C6E9-4424-BE9C-C056B2DD5CB4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8829,7 +8829,7 @@
         <xdr:cNvPr id="4400" name="Grafik 56">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE2D2220-BC12-891F-D9CF-4C7F9BB38D3E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EBF91D2-E0E6-1D05-E6C3-7F083FADA203}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8903,7 +8903,7 @@
         <xdr:cNvPr id="4401" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{658F667B-DEB1-2B13-31AC-1A2B5ACD10D1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26568137-6BFE-2BB5-EE0C-766CBD7FC74E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8977,7 +8977,7 @@
         <xdr:cNvPr id="4402" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{670F507C-9FBE-1691-D304-5F462B30A156}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{110D1A7D-5F97-791E-FD4B-207484C23120}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9051,7 +9051,7 @@
         <xdr:cNvPr id="4403" name="Grafik 56">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9BEC59F-1295-023E-2B34-D44FF3D54DB4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC79426E-7F0B-E118-019F-F4B7D359AF80}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9125,7 +9125,7 @@
         <xdr:cNvPr id="4404" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4AD438CE-08ED-672F-8D6B-C0036AC5309B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A32DE50F-3914-0EA7-63E8-0F115159A7C2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9199,7 +9199,7 @@
         <xdr:cNvPr id="4405" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{694E591F-1760-DC47-219C-E7186D0ACED6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{287DC1FC-0498-DFFE-5A58-747767FB024B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9273,7 +9273,7 @@
         <xdr:cNvPr id="4406" name="Grafik 56">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C676C4D-28B0-9A1E-0BDD-6E7D7753D342}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F222892C-11C8-0B18-AFE6-9AAB880D1CF2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9347,7 +9347,7 @@
         <xdr:cNvPr id="4407" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4AF5C76-4873-66B6-3DD4-1F404FB8B470}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{058ECCE6-0BAF-5B6F-B9D9-89D4B539B711}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9421,7 +9421,7 @@
         <xdr:cNvPr id="4408" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E489E91-BFF0-72E5-B4A3-02DD679CE871}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{466C45F9-404E-2DBF-58D1-32DEA75E7453}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9495,7 +9495,7 @@
         <xdr:cNvPr id="4409" name="Grafik 56">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79CE1006-470A-AB01-B43B-403A6EE28F32}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5FA76C2-7E9E-8B21-AAC8-FF6435F9F80A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9569,7 +9569,7 @@
         <xdr:cNvPr id="4410" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{755DE398-5FE3-5194-230C-2A146E2C895C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FD3E9DC-96D2-494B-E9A1-4702AFABCE72}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9643,7 +9643,7 @@
         <xdr:cNvPr id="4411" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C06F3C7F-E506-169C-BC8C-1C8EA1E553B6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1885D55-A462-2080-1FA4-E0E8C4BD2CDB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9717,7 +9717,7 @@
         <xdr:cNvPr id="4412" name="Grafik 56">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92BC4DA4-3877-259C-90C2-0223C04D582A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A06C21AE-6B1C-B85C-39C7-79D14E5A57BE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9791,7 +9791,7 @@
         <xdr:cNvPr id="4413" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99A2C580-8D8A-6344-7705-4ECE33FD916C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99B96FC8-8843-07B9-F9E2-AFE67266D208}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9865,7 +9865,7 @@
         <xdr:cNvPr id="4414" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92C68008-0273-756B-EC93-A14E407FF5AD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DD6A590-BB3A-BBE6-8423-444BA3A19D07}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9939,7 +9939,7 @@
         <xdr:cNvPr id="4415" name="Grafik 56">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3496126D-B211-E7B6-C02E-03DCDA9CB4B3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E3D2DE9-90A7-A474-736A-F52A39D2CCEB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10013,7 +10013,7 @@
         <xdr:cNvPr id="4416" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAF2192D-93EC-9B88-E1DE-3EF7BA31B0F6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECAF7EA1-41BC-BDC1-AA0F-69BD9A347A8D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10087,7 +10087,7 @@
         <xdr:cNvPr id="4417" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C0C9ED1-81F2-8589-1289-95D22E24E58F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53041D1E-444B-6933-E64E-FBC2CB743455}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10161,7 +10161,7 @@
         <xdr:cNvPr id="4418" name="Grafik 56">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{568039C1-19A0-D2E0-06B2-C78D02FB5F60}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17AE333C-EE79-3111-7EDC-2603D752857D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10235,7 +10235,7 @@
         <xdr:cNvPr id="4419" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3DEEDB9-6920-5613-FC82-F742C4ECBDD2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A4E0ECE-EFE0-2D18-8909-9CF0ABE13608}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10309,7 +10309,7 @@
         <xdr:cNvPr id="4420" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3944BF5D-17DF-0DD4-B033-D9001D83FBDD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD232201-4AE1-8E77-C651-B3C17A8C1E49}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10383,7 +10383,7 @@
         <xdr:cNvPr id="4421" name="Grafik 56">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C74EAB4-E047-495C-E006-C307BCC89562}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66F6573F-D7A5-B3E6-09CF-FC750E37768B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10457,7 +10457,7 @@
         <xdr:cNvPr id="4422" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{052F7320-03DE-F2D0-94A9-C81F92893775}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD0AE93D-05EB-E14A-3777-0FF2EADFB963}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10531,7 +10531,7 @@
         <xdr:cNvPr id="4423" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65BB9FCF-068E-D522-2FB9-AEF571364039}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6294233E-D0A0-FEF3-B08B-67834C100BC0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10605,7 +10605,7 @@
         <xdr:cNvPr id="4424" name="Grafik 56">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F81297E7-9864-E54C-823A-F29F8864722C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91BC1C5C-8F20-5127-BFD7-F3F7C79F7C3D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10679,7 +10679,7 @@
         <xdr:cNvPr id="4425" name="Grafik 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB52CD46-0A18-0A5D-D5EE-0A34385D01BF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C9E63C9-EBBC-BE4B-5015-7CF2BF8CA3C4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10753,7 +10753,7 @@
         <xdr:cNvPr id="4426" name="Grafik 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8E8196C-B12D-DA01-6712-AD9C1F22D7E8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83D4A75D-2CF2-5C78-4DB0-E28CA1E76CF2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11098,7 +11098,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B341D104-BCB6-4235-8D5D-EE84A8B57396}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AED17842-72EF-4B1A-B9BD-5BCD79276E55}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -11253,7 +11253,7 @@
       </c>
       <c r="S2" s="16"/>
       <c r="T2" s="18" t="str">
-        <f>IF(C35&gt;18,IF(C35=20,_NW20,IF(C35=60,U4,IF(C35=50,_NW50,IF(C35=25,_NW25,IF(C35=32,_NW32,IF(C35=40,_NW40,"&gt;")))))),IF(C35=8,_NW8,IF(C35=6,_NW6,IF(C35=10,_NW10,IF(C35=18,_NW18,IF(C35=16,_NW16,IF(C35=12,_NW12,"")))))))</f>
+        <f>IF(C35&gt;18,IF(C35=20,Nennweite20,IF(C35=60,U4,IF(C35=50,Nennweite50,IF(C35=25,Nennweite25,IF(C35=32,Nennweite32,IF(C35=40,Nennweite40,"&gt;")))))),IF(C35=8,Nennweite8,IF(C35=6,Nennweite6,IF(C35=10,Nennweite10,IF(C35=18,Nennweite18,IF(C35=16,Nennweite16,IF(C35=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U2" s="16" t="s">
@@ -12640,7 +12640,7 @@
       </c>
       <c r="S32" s="16"/>
       <c r="T32" s="18" t="str">
-        <f>IF(C65&gt;18,IF(C65=20,_NW20,IF(C65=60,U34,IF(C65=50,_NW50,IF(C65=25,_NW25,IF(C65=32,_NW32,IF(C65=40,_NW40,"&gt;")))))),IF(C65=8,_NW8,IF(C65=6,_NW6,IF(C65=10,_NW10,IF(C65=18,_NW18,IF(C65=16,_NW16,IF(C65=12,_NW12,"")))))))</f>
+        <f>IF(C65&gt;18,IF(C65=20,Nennweite20,IF(C65=60,U34,IF(C65=50,Nennweite50,IF(C65=25,Nennweite25,IF(C65=32,Nennweite32,IF(C65=40,Nennweite40,"&gt;")))))),IF(C65=8,Nennweite8,IF(C65=6,Nennweite6,IF(C65=10,Nennweite10,IF(C65=18,Nennweite18,IF(C65=16,Nennweite16,IF(C65=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U32" s="16" t="s">
@@ -13912,7 +13912,7 @@
       </c>
       <c r="S62" s="16"/>
       <c r="T62" s="18" t="str">
-        <f>IF(C95&gt;18,IF(C95=20,_NW20,IF(C95=60,U64,IF(C95=50,_NW50,IF(C95=25,_NW25,IF(C95=32,_NW32,IF(C95=40,_NW40,"&gt;")))))),IF(C95=8,_NW8,IF(C95=6,_NW6,IF(C95=10,_NW10,IF(C95=18,_NW18,IF(C95=16,_NW16,IF(C95=12,_NW12,"")))))))</f>
+        <f>IF(C95&gt;18,IF(C95=20,Nennweite20,IF(C95=60,U64,IF(C95=50,Nennweite50,IF(C95=25,Nennweite25,IF(C95=32,Nennweite32,IF(C95=40,Nennweite40,"&gt;")))))),IF(C95=8,Nennweite8,IF(C95=6,Nennweite6,IF(C95=10,Nennweite10,IF(C95=18,Nennweite18,IF(C95=16,Nennweite16,IF(C95=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U62" s="16" t="s">
@@ -14947,7 +14947,7 @@
       </c>
       <c r="S92" s="16"/>
       <c r="T92" s="18" t="str">
-        <f>IF(C125&gt;18,IF(C125=20,_NW20,IF(C125=60,U94,IF(C125=50,_NW50,IF(C125=25,_NW25,IF(C125=32,_NW32,IF(C125=40,_NW40,"&gt;")))))),IF(C125=8,_NW8,IF(C125=6,_NW6,IF(C125=10,_NW10,IF(C125=18,_NW18,IF(C125=16,_NW16,IF(C125=12,_NW12,"")))))))</f>
+        <f>IF(C125&gt;18,IF(C125=20,Nennweite20,IF(C125=60,U94,IF(C125=50,Nennweite50,IF(C125=25,Nennweite25,IF(C125=32,Nennweite32,IF(C125=40,Nennweite40,"&gt;")))))),IF(C125=8,Nennweite8,IF(C125=6,Nennweite6,IF(C125=10,Nennweite10,IF(C125=18,Nennweite18,IF(C125=16,Nennweite16,IF(C125=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U92" s="16" t="s">
@@ -15937,7 +15937,7 @@
       </c>
       <c r="S122" s="16"/>
       <c r="T122" s="18" t="str">
-        <f>IF(C155&gt;18,IF(C155=20,_NW20,IF(C155=60,U124,IF(C155=50,_NW50,IF(C155=25,_NW25,IF(C155=32,_NW32,IF(C155=40,_NW40,"&gt;")))))),IF(C155=8,_NW8,IF(C155=6,_NW6,IF(C155=10,_NW10,IF(C155=18,_NW18,IF(C155=16,_NW16,IF(C155=12,_NW12,"")))))))</f>
+        <f>IF(C155&gt;18,IF(C155=20,Nennweite20,IF(C155=60,U124,IF(C155=50,Nennweite50,IF(C155=25,Nennweite25,IF(C155=32,Nennweite32,IF(C155=40,Nennweite40,"&gt;")))))),IF(C155=8,Nennweite8,IF(C155=6,Nennweite6,IF(C155=10,Nennweite10,IF(C155=18,Nennweite18,IF(C155=16,Nennweite16,IF(C155=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U122" s="16" t="s">
@@ -16927,7 +16927,7 @@
       </c>
       <c r="S152" s="16"/>
       <c r="T152" s="18" t="str">
-        <f>IF(C185&gt;18,IF(C185=20,_NW20,IF(C185=60,U154,IF(C185=50,_NW50,IF(C185=25,_NW25,IF(C185=32,_NW32,IF(C185=40,_NW40,"&gt;")))))),IF(C185=8,_NW8,IF(C185=6,_NW6,IF(C185=10,_NW10,IF(C185=18,_NW18,IF(C185=16,_NW16,IF(C185=12,_NW12,"")))))))</f>
+        <f>IF(C185&gt;18,IF(C185=20,Nennweite20,IF(C185=60,U154,IF(C185=50,Nennweite50,IF(C185=25,Nennweite25,IF(C185=32,Nennweite32,IF(C185=40,Nennweite40,"&gt;")))))),IF(C185=8,Nennweite8,IF(C185=6,Nennweite6,IF(C185=10,Nennweite10,IF(C185=18,Nennweite18,IF(C185=16,Nennweite16,IF(C185=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U152" s="16" t="s">
@@ -18361,7 +18361,7 @@
       </c>
       <c r="S182" s="16"/>
       <c r="T182" s="18" t="str">
-        <f>IF(C215&gt;18,IF(C215=20,_NW20,IF(C215=60,U184,IF(C215=50,_NW50,IF(C215=25,_NW25,IF(C215=32,_NW32,IF(C215=40,_NW40,"&gt;")))))),IF(C215=8,_NW8,IF(C215=6,_NW6,IF(C215=10,_NW10,IF(C215=18,_NW18,IF(C215=16,_NW16,IF(C215=12,_NW12,"")))))))</f>
+        <f>IF(C215&gt;18,IF(C215=20,Nennweite20,IF(C215=60,U184,IF(C215=50,Nennweite50,IF(C215=25,Nennweite25,IF(C215=32,Nennweite32,IF(C215=40,Nennweite40,"&gt;")))))),IF(C215=8,Nennweite8,IF(C215=6,Nennweite6,IF(C215=10,Nennweite10,IF(C215=18,Nennweite18,IF(C215=16,Nennweite16,IF(C215=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U182" s="16" t="s">
@@ -19795,7 +19795,7 @@
       </c>
       <c r="S212" s="16"/>
       <c r="T212" s="18" t="str">
-        <f>IF(C245&gt;18,IF(C245=20,_NW20,IF(C245=60,U214,IF(C245=50,_NW50,IF(C245=25,_NW25,IF(C245=32,_NW32,IF(C245=40,_NW40,"&gt;")))))),IF(C245=8,_NW8,IF(C245=6,_NW6,IF(C245=10,_NW10,IF(C245=18,_NW18,IF(C245=16,_NW16,IF(C245=12,_NW12,"")))))))</f>
+        <f>IF(C245&gt;18,IF(C245=20,Nennweite20,IF(C245=60,U214,IF(C245=50,Nennweite50,IF(C245=25,Nennweite25,IF(C245=32,Nennweite32,IF(C245=40,Nennweite40,"&gt;")))))),IF(C245=8,Nennweite8,IF(C245=6,Nennweite6,IF(C245=10,Nennweite10,IF(C245=18,Nennweite18,IF(C245=16,Nennweite16,IF(C245=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U212" s="16" t="s">
@@ -21229,7 +21229,7 @@
       </c>
       <c r="S242" s="16"/>
       <c r="T242" s="18" t="str">
-        <f>IF(C275&gt;18,IF(C275=20,_NW20,IF(C275=60,U244,IF(C275=50,_NW50,IF(C275=25,_NW25,IF(C275=32,_NW32,IF(C275=40,_NW40,"&gt;")))))),IF(C275=8,_NW8,IF(C275=6,_NW6,IF(C275=10,_NW10,IF(C275=18,_NW18,IF(C275=16,_NW16,IF(C275=12,_NW12,"")))))))</f>
+        <f>IF(C275&gt;18,IF(C275=20,Nennweite20,IF(C275=60,U244,IF(C275=50,Nennweite50,IF(C275=25,Nennweite25,IF(C275=32,Nennweite32,IF(C275=40,Nennweite40,"&gt;")))))),IF(C275=8,Nennweite8,IF(C275=6,Nennweite6,IF(C275=10,Nennweite10,IF(C275=18,Nennweite18,IF(C275=16,Nennweite16,IF(C275=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U242" s="16" t="s">
@@ -22663,7 +22663,7 @@
       </c>
       <c r="S272" s="16"/>
       <c r="T272" s="18" t="str">
-        <f>IF(C305&gt;18,IF(C305=20,_NW20,IF(C305=60,U274,IF(C305=50,_NW50,IF(C305=25,_NW25,IF(C305=32,_NW32,IF(C305=40,_NW40,"&gt;")))))),IF(C305=8,_NW8,IF(C305=6,_NW6,IF(C305=10,_NW10,IF(C305=18,_NW18,IF(C305=16,_NW16,IF(C305=12,_NW12,"")))))))</f>
+        <f>IF(C305&gt;18,IF(C305=20,Nennweite20,IF(C305=60,U274,IF(C305=50,Nennweite50,IF(C305=25,Nennweite25,IF(C305=32,Nennweite32,IF(C305=40,Nennweite40,"&gt;")))))),IF(C305=8,Nennweite8,IF(C305=6,Nennweite6,IF(C305=10,Nennweite10,IF(C305=18,Nennweite18,IF(C305=16,Nennweite16,IF(C305=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U272" s="16" t="s">
@@ -24097,7 +24097,7 @@
       </c>
       <c r="S302" s="16"/>
       <c r="T302" s="18" t="str">
-        <f>IF(C335&gt;18,IF(C335=20,_NW20,IF(C335=60,U304,IF(C335=50,_NW50,IF(C335=25,_NW25,IF(C335=32,_NW32,IF(C335=40,_NW40,"&gt;")))))),IF(C335=8,_NW8,IF(C335=6,_NW6,IF(C335=10,_NW10,IF(C335=18,_NW18,IF(C335=16,_NW16,IF(C335=12,_NW12,"")))))))</f>
+        <f>IF(C335&gt;18,IF(C335=20,Nennweite20,IF(C335=60,U304,IF(C335=50,Nennweite50,IF(C335=25,Nennweite25,IF(C335=32,Nennweite32,IF(C335=40,Nennweite40,"&gt;")))))),IF(C335=8,Nennweite8,IF(C335=6,Nennweite6,IF(C335=10,Nennweite10,IF(C335=18,Nennweite18,IF(C335=16,Nennweite16,IF(C335=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U302" s="16" t="s">
@@ -25531,7 +25531,7 @@
       </c>
       <c r="S332" s="16"/>
       <c r="T332" s="18" t="str">
-        <f>IF(C365&gt;18,IF(C365=20,_NW20,IF(C365=60,U334,IF(C365=50,_NW50,IF(C365=25,_NW25,IF(C365=32,_NW32,IF(C365=40,_NW40,"&gt;")))))),IF(C365=8,_NW8,IF(C365=6,_NW6,IF(C365=10,_NW10,IF(C365=18,_NW18,IF(C365=16,_NW16,IF(C365=12,_NW12,"")))))))</f>
+        <f>IF(C365&gt;18,IF(C365=20,Nennweite20,IF(C365=60,U334,IF(C365=50,Nennweite50,IF(C365=25,Nennweite25,IF(C365=32,Nennweite32,IF(C365=40,Nennweite40,"&gt;")))))),IF(C365=8,Nennweite8,IF(C365=6,Nennweite6,IF(C365=10,Nennweite10,IF(C365=18,Nennweite18,IF(C365=16,Nennweite16,IF(C365=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U332" s="16" t="s">
@@ -26965,7 +26965,7 @@
       </c>
       <c r="S362" s="16"/>
       <c r="T362" s="18" t="str">
-        <f>IF(C395&gt;18,IF(C395=20,_NW20,IF(C395=60,U364,IF(C395=50,_NW50,IF(C395=25,_NW25,IF(C395=32,_NW32,IF(C395=40,_NW40,"&gt;")))))),IF(C395=8,_NW8,IF(C395=6,_NW6,IF(C395=10,_NW10,IF(C395=18,_NW18,IF(C395=16,_NW16,IF(C395=12,_NW12,"")))))))</f>
+        <f>IF(C395&gt;18,IF(C395=20,Nennweite20,IF(C395=60,U364,IF(C395=50,Nennweite50,IF(C395=25,Nennweite25,IF(C395=32,Nennweite32,IF(C395=40,Nennweite40,"&gt;")))))),IF(C395=8,Nennweite8,IF(C395=6,Nennweite6,IF(C395=10,Nennweite10,IF(C395=18,Nennweite18,IF(C395=16,Nennweite16,IF(C395=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U362" s="16" t="s">
@@ -28398,7 +28398,7 @@
       </c>
       <c r="S392" s="16"/>
       <c r="T392" s="18" t="str">
-        <f>IF(C425&gt;18,IF(C425=20,_NW20,IF(C425=60,U394,IF(C425=50,_NW50,IF(C425=25,_NW25,IF(C425=32,_NW32,IF(C425=40,_NW40,"&gt;")))))),IF(C425=8,_NW8,IF(C425=6,_NW6,IF(C425=10,_NW10,IF(C425=18,_NW18,IF(C425=16,_NW16,IF(C425=12,_NW12,"")))))))</f>
+        <f>IF(C425&gt;18,IF(C425=20,Nennweite20,IF(C425=60,U394,IF(C425=50,Nennweite50,IF(C425=25,Nennweite25,IF(C425=32,Nennweite32,IF(C425=40,Nennweite40,"&gt;")))))),IF(C425=8,Nennweite8,IF(C425=6,Nennweite6,IF(C425=10,Nennweite10,IF(C425=18,Nennweite18,IF(C425=16,Nennweite16,IF(C425=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U392" s="16" t="s">
@@ -29670,7 +29670,7 @@
       </c>
       <c r="S422" s="16"/>
       <c r="T422" s="18" t="str">
-        <f>IF(C455&gt;18,IF(C455=20,_NW20,IF(C455=60,U424,IF(C455=50,_NW50,IF(C455=25,_NW25,IF(C455=32,_NW32,IF(C455=40,_NW40,"&gt;")))))),IF(C455=8,_NW8,IF(C455=6,_NW6,IF(C455=10,_NW10,IF(C455=18,_NW18,IF(C455=16,_NW16,IF(C455=12,_NW12,"")))))))</f>
+        <f>IF(C455&gt;18,IF(C455=20,Nennweite20,IF(C455=60,U424,IF(C455=50,Nennweite50,IF(C455=25,Nennweite25,IF(C455=32,Nennweite32,IF(C455=40,Nennweite40,"&gt;")))))),IF(C455=8,Nennweite8,IF(C455=6,Nennweite6,IF(C455=10,Nennweite10,IF(C455=18,Nennweite18,IF(C455=16,Nennweite16,IF(C455=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U422" s="16" t="s">
@@ -30705,7 +30705,7 @@
       </c>
       <c r="S452" s="16"/>
       <c r="T452" s="18" t="str">
-        <f>IF(C485&gt;18,IF(C485=20,_NW20,IF(C485=60,U454,IF(C485=50,_NW50,IF(C485=25,_NW25,IF(C485=32,_NW32,IF(C485=40,_NW40,"&gt;")))))),IF(C485=8,_NW8,IF(C485=6,_NW6,IF(C485=10,_NW10,IF(C485=18,_NW18,IF(C485=16,_NW16,IF(C485=12,_NW12,"")))))))</f>
+        <f>IF(C485&gt;18,IF(C485=20,Nennweite20,IF(C485=60,U454,IF(C485=50,Nennweite50,IF(C485=25,Nennweite25,IF(C485=32,Nennweite32,IF(C485=40,Nennweite40,"&gt;")))))),IF(C485=8,Nennweite8,IF(C485=6,Nennweite6,IF(C485=10,Nennweite10,IF(C485=18,Nennweite18,IF(C485=16,Nennweite16,IF(C485=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U452" s="16" t="s">
@@ -31695,7 +31695,7 @@
       </c>
       <c r="S482" s="16"/>
       <c r="T482" s="18" t="str">
-        <f>IF(C515&gt;18,IF(C515=20,_NW20,IF(C515=60,U484,IF(C515=50,_NW50,IF(C515=25,_NW25,IF(C515=32,_NW32,IF(C515=40,_NW40,"&gt;")))))),IF(C515=8,_NW8,IF(C515=6,_NW6,IF(C515=10,_NW10,IF(C515=18,_NW18,IF(C515=16,_NW16,IF(C515=12,_NW12,"")))))))</f>
+        <f>IF(C515&gt;18,IF(C515=20,Nennweite20,IF(C515=60,U484,IF(C515=50,Nennweite50,IF(C515=25,Nennweite25,IF(C515=32,Nennweite32,IF(C515=40,Nennweite40,"&gt;")))))),IF(C515=8,Nennweite8,IF(C515=6,Nennweite6,IF(C515=10,Nennweite10,IF(C515=18,Nennweite18,IF(C515=16,Nennweite16,IF(C515=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U482" s="16" t="s">
@@ -32685,7 +32685,7 @@
       </c>
       <c r="S512" s="16"/>
       <c r="T512" s="18" t="str">
-        <f>IF(C545&gt;18,IF(C545=20,_NW20,IF(C545=60,U514,IF(C545=50,_NW50,IF(C545=25,_NW25,IF(C545=32,_NW32,IF(C545=40,_NW40,"&gt;")))))),IF(C545=8,_NW8,IF(C545=6,_NW6,IF(C545=10,_NW10,IF(C545=18,_NW18,IF(C545=16,_NW16,IF(C545=12,_NW12,"")))))))</f>
+        <f>IF(C545&gt;18,IF(C545=20,Nennweite20,IF(C545=60,U514,IF(C545=50,Nennweite50,IF(C545=25,Nennweite25,IF(C545=32,Nennweite32,IF(C545=40,Nennweite40,"&gt;")))))),IF(C545=8,Nennweite8,IF(C545=6,Nennweite6,IF(C545=10,Nennweite10,IF(C545=18,Nennweite18,IF(C545=16,Nennweite16,IF(C545=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U512" s="16" t="s">
@@ -34119,7 +34119,7 @@
       </c>
       <c r="S542" s="16"/>
       <c r="T542" s="18" t="str">
-        <f>IF(C575&gt;18,IF(C575=20,_NW20,IF(C575=60,U544,IF(C575=50,_NW50,IF(C575=25,_NW25,IF(C575=32,_NW32,IF(C575=40,_NW40,"&gt;")))))),IF(C575=8,_NW8,IF(C575=6,_NW6,IF(C575=10,_NW10,IF(C575=18,_NW18,IF(C575=16,_NW16,IF(C575=12,_NW12,"")))))))</f>
+        <f>IF(C575&gt;18,IF(C575=20,Nennweite20,IF(C575=60,U544,IF(C575=50,Nennweite50,IF(C575=25,Nennweite25,IF(C575=32,Nennweite32,IF(C575=40,Nennweite40,"&gt;")))))),IF(C575=8,Nennweite8,IF(C575=6,Nennweite6,IF(C575=10,Nennweite10,IF(C575=18,Nennweite18,IF(C575=16,Nennweite16,IF(C575=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U542" s="16" t="s">
@@ -35553,7 +35553,7 @@
       </c>
       <c r="S572" s="16"/>
       <c r="T572" s="18" t="str">
-        <f>IF(C605&gt;18,IF(C605=20,_NW20,IF(C605=60,U574,IF(C605=50,_NW50,IF(C605=25,_NW25,IF(C605=32,_NW32,IF(C605=40,_NW40,"&gt;")))))),IF(C605=8,_NW8,IF(C605=6,_NW6,IF(C605=10,_NW10,IF(C605=18,_NW18,IF(C605=16,_NW16,IF(C605=12,_NW12,"")))))))</f>
+        <f>IF(C605&gt;18,IF(C605=20,Nennweite20,IF(C605=60,U574,IF(C605=50,Nennweite50,IF(C605=25,Nennweite25,IF(C605=32,Nennweite32,IF(C605=40,Nennweite40,"&gt;")))))),IF(C605=8,Nennweite8,IF(C605=6,Nennweite6,IF(C605=10,Nennweite10,IF(C605=18,Nennweite18,IF(C605=16,Nennweite16,IF(C605=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U572" s="16" t="s">
@@ -36987,7 +36987,7 @@
       </c>
       <c r="S602" s="16"/>
       <c r="T602" s="18" t="str">
-        <f>IF(C635&gt;18,IF(C635=20,_NW20,IF(C635=60,U604,IF(C635=50,_NW50,IF(C635=25,_NW25,IF(C635=32,_NW32,IF(C635=40,_NW40,"&gt;")))))),IF(C635=8,_NW8,IF(C635=6,_NW6,IF(C635=10,_NW10,IF(C635=18,_NW18,IF(C635=16,_NW16,IF(C635=12,_NW12,"")))))))</f>
+        <f>IF(C635&gt;18,IF(C635=20,Nennweite20,IF(C635=60,U604,IF(C635=50,Nennweite50,IF(C635=25,Nennweite25,IF(C635=32,Nennweite32,IF(C635=40,Nennweite40,"&gt;")))))),IF(C635=8,Nennweite8,IF(C635=6,Nennweite6,IF(C635=10,Nennweite10,IF(C635=18,Nennweite18,IF(C635=16,Nennweite16,IF(C635=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U602" s="16" t="s">
@@ -38421,7 +38421,7 @@
       </c>
       <c r="S632" s="16"/>
       <c r="T632" s="18" t="str">
-        <f>IF(C665&gt;18,IF(C665=20,_NW20,IF(C665=60,U634,IF(C665=50,_NW50,IF(C665=25,_NW25,IF(C665=32,_NW32,IF(C665=40,_NW40,"&gt;")))))),IF(C665=8,_NW8,IF(C665=6,_NW6,IF(C665=10,_NW10,IF(C665=18,_NW18,IF(C665=16,_NW16,IF(C665=12,_NW12,"")))))))</f>
+        <f>IF(C665&gt;18,IF(C665=20,Nennweite20,IF(C665=60,U634,IF(C665=50,Nennweite50,IF(C665=25,Nennweite25,IF(C665=32,Nennweite32,IF(C665=40,Nennweite40,"&gt;")))))),IF(C665=8,Nennweite8,IF(C665=6,Nennweite6,IF(C665=10,Nennweite10,IF(C665=18,Nennweite18,IF(C665=16,Nennweite16,IF(C665=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U632" s="16" t="s">
@@ -39855,7 +39855,7 @@
       </c>
       <c r="S662" s="16"/>
       <c r="T662" s="18" t="str">
-        <f>IF(C695&gt;18,IF(C695=20,_NW20,IF(C695=60,U664,IF(C695=50,_NW50,IF(C695=25,_NW25,IF(C695=32,_NW32,IF(C695=40,_NW40,"&gt;")))))),IF(C695=8,_NW8,IF(C695=6,_NW6,IF(C695=10,_NW10,IF(C695=18,_NW18,IF(C695=16,_NW16,IF(C695=12,_NW12,"")))))))</f>
+        <f>IF(C695&gt;18,IF(C695=20,Nennweite20,IF(C695=60,U664,IF(C695=50,Nennweite50,IF(C695=25,Nennweite25,IF(C695=32,Nennweite32,IF(C695=40,Nennweite40,"&gt;")))))),IF(C695=8,Nennweite8,IF(C695=6,Nennweite6,IF(C695=10,Nennweite10,IF(C695=18,Nennweite18,IF(C695=16,Nennweite16,IF(C695=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U662" s="16" t="s">
@@ -41289,7 +41289,7 @@
       </c>
       <c r="S692" s="16"/>
       <c r="T692" s="18" t="str">
-        <f>IF(C725&gt;18,IF(C725=20,_NW20,IF(C725=60,U694,IF(C725=50,_NW50,IF(C725=25,_NW25,IF(C725=32,_NW32,IF(C725=40,_NW40,"&gt;")))))),IF(C725=8,_NW8,IF(C725=6,_NW6,IF(C725=10,_NW10,IF(C725=18,_NW18,IF(C725=16,_NW16,IF(C725=12,_NW12,"")))))))</f>
+        <f>IF(C725&gt;18,IF(C725=20,Nennweite20,IF(C725=60,U694,IF(C725=50,Nennweite50,IF(C725=25,Nennweite25,IF(C725=32,Nennweite32,IF(C725=40,Nennweite40,"&gt;")))))),IF(C725=8,Nennweite8,IF(C725=6,Nennweite6,IF(C725=10,Nennweite10,IF(C725=18,Nennweite18,IF(C725=16,Nennweite16,IF(C725=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U692" s="16" t="s">
@@ -42723,7 +42723,7 @@
       </c>
       <c r="S722" s="16"/>
       <c r="T722" s="18" t="str">
-        <f>IF(C755&gt;18,IF(C755=20,_NW20,IF(C755=60,U724,IF(C755=50,_NW50,IF(C755=25,_NW25,IF(C755=32,_NW32,IF(C755=40,_NW40,"&gt;")))))),IF(C755=8,_NW8,IF(C755=6,_NW6,IF(C755=10,_NW10,IF(C755=18,_NW18,IF(C755=16,_NW16,IF(C755=12,_NW12,"")))))))</f>
+        <f>IF(C755&gt;18,IF(C755=20,Nennweite20,IF(C755=60,U724,IF(C755=50,Nennweite50,IF(C755=25,Nennweite25,IF(C755=32,Nennweite32,IF(C755=40,Nennweite40,"&gt;")))))),IF(C755=8,Nennweite8,IF(C755=6,Nennweite6,IF(C755=10,Nennweite10,IF(C755=18,Nennweite18,IF(C755=16,Nennweite16,IF(C755=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U722" s="16" t="s">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="S752" s="16"/>
       <c r="T752" s="18" t="str">
-        <f>IF(C785&gt;18,IF(C785=20,_NW20,IF(C785=60,U754,IF(C785=50,_NW50,IF(C785=25,_NW25,IF(C785=32,_NW32,IF(C785=40,_NW40,"&gt;")))))),IF(C785=8,_NW8,IF(C785=6,_NW6,IF(C785=10,_NW10,IF(C785=18,_NW18,IF(C785=16,_NW16,IF(C785=12,_NW12,"")))))))</f>
+        <f>IF(C785&gt;18,IF(C785=20,Nennweite20,IF(C785=60,U754,IF(C785=50,Nennweite50,IF(C785=25,Nennweite25,IF(C785=32,Nennweite32,IF(C785=40,Nennweite40,"&gt;")))))),IF(C785=8,Nennweite8,IF(C785=6,Nennweite6,IF(C785=10,Nennweite10,IF(C785=18,Nennweite18,IF(C785=16,Nennweite16,IF(C785=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U752" s="16" t="s">
@@ -45591,7 +45591,7 @@
       </c>
       <c r="S782" s="16"/>
       <c r="T782" s="18" t="str">
-        <f>IF(C815&gt;18,IF(C815=20,_NW20,IF(C815=60,U784,IF(C815=50,_NW50,IF(C815=25,_NW25,IF(C815=32,_NW32,IF(C815=40,_NW40,"&gt;")))))),IF(C815=8,_NW8,IF(C815=6,_NW6,IF(C815=10,_NW10,IF(C815=18,_NW18,IF(C815=16,_NW16,IF(C815=12,_NW12,"")))))))</f>
+        <f>IF(C815&gt;18,IF(C815=20,Nennweite20,IF(C815=60,U784,IF(C815=50,Nennweite50,IF(C815=25,Nennweite25,IF(C815=32,Nennweite32,IF(C815=40,Nennweite40,"&gt;")))))),IF(C815=8,Nennweite8,IF(C815=6,Nennweite6,IF(C815=10,Nennweite10,IF(C815=18,Nennweite18,IF(C815=16,Nennweite16,IF(C815=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U782" s="16" t="s">
@@ -47025,7 +47025,7 @@
       </c>
       <c r="S812" s="16"/>
       <c r="T812" s="18" t="str">
-        <f>IF(C845&gt;18,IF(C845=20,_NW20,IF(C845=60,U814,IF(C845=50,_NW50,IF(C845=25,_NW25,IF(C845=32,_NW32,IF(C845=40,_NW40,"&gt;")))))),IF(C845=8,_NW8,IF(C845=6,_NW6,IF(C845=10,_NW10,IF(C845=18,_NW18,IF(C845=16,_NW16,IF(C845=12,_NW12,"")))))))</f>
+        <f>IF(C845&gt;18,IF(C845=20,Nennweite20,IF(C845=60,U814,IF(C845=50,Nennweite50,IF(C845=25,Nennweite25,IF(C845=32,Nennweite32,IF(C845=40,Nennweite40,"&gt;")))))),IF(C845=8,Nennweite8,IF(C845=6,Nennweite6,IF(C845=10,Nennweite10,IF(C845=18,Nennweite18,IF(C845=16,Nennweite16,IF(C845=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U812" s="16" t="s">
@@ -48459,7 +48459,7 @@
       </c>
       <c r="S842" s="16"/>
       <c r="T842" s="18" t="str">
-        <f>IF(C875&gt;18,IF(C875=20,_NW20,IF(C875=60,U844,IF(C875=50,_NW50,IF(C875=25,_NW25,IF(C875=32,_NW32,IF(C875=40,_NW40,"&gt;")))))),IF(C875=8,_NW8,IF(C875=6,_NW6,IF(C875=10,_NW10,IF(C875=18,_NW18,IF(C875=16,_NW16,IF(C875=12,_NW12,"")))))))</f>
+        <f>IF(C875&gt;18,IF(C875=20,Nennweite20,IF(C875=60,U844,IF(C875=50,Nennweite50,IF(C875=25,Nennweite25,IF(C875=32,Nennweite32,IF(C875=40,Nennweite40,"&gt;")))))),IF(C875=8,Nennweite8,IF(C875=6,Nennweite6,IF(C875=10,Nennweite10,IF(C875=18,Nennweite18,IF(C875=16,Nennweite16,IF(C875=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U842" s="16" t="s">
@@ -49893,7 +49893,7 @@
       </c>
       <c r="S872" s="16"/>
       <c r="T872" s="18" t="str">
-        <f>IF(C905&gt;18,IF(C905=20,_NW20,IF(C905=60,U874,IF(C905=50,_NW50,IF(C905=25,_NW25,IF(C905=32,_NW32,IF(C905=40,_NW40,"&gt;")))))),IF(C905=8,_NW8,IF(C905=6,_NW6,IF(C905=10,_NW10,IF(C905=18,_NW18,IF(C905=16,_NW16,IF(C905=12,_NW12,"")))))))</f>
+        <f>IF(C905&gt;18,IF(C905=20,Nennweite20,IF(C905=60,U874,IF(C905=50,Nennweite50,IF(C905=25,Nennweite25,IF(C905=32,Nennweite32,IF(C905=40,Nennweite40,"&gt;")))))),IF(C905=8,Nennweite8,IF(C905=6,Nennweite6,IF(C905=10,Nennweite10,IF(C905=18,Nennweite18,IF(C905=16,Nennweite16,IF(C905=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U872" s="16" t="s">
@@ -51327,7 +51327,7 @@
       </c>
       <c r="S902" s="16"/>
       <c r="T902" s="18" t="str">
-        <f>IF(C935&gt;18,IF(C935=20,_NW20,IF(C935=60,U904,IF(C935=50,_NW50,IF(C935=25,_NW25,IF(C935=32,_NW32,IF(C935=40,_NW40,"&gt;")))))),IF(C935=8,_NW8,IF(C935=6,_NW6,IF(C935=10,_NW10,IF(C935=18,_NW18,IF(C935=16,_NW16,IF(C935=12,_NW12,"")))))))</f>
+        <f>IF(C935&gt;18,IF(C935=20,Nennweite20,IF(C935=60,U904,IF(C935=50,Nennweite50,IF(C935=25,Nennweite25,IF(C935=32,Nennweite32,IF(C935=40,Nennweite40,"&gt;")))))),IF(C935=8,Nennweite8,IF(C935=6,Nennweite6,IF(C935=10,Nennweite10,IF(C935=18,Nennweite18,IF(C935=16,Nennweite16,IF(C935=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U902" s="16" t="s">
@@ -52761,7 +52761,7 @@
       </c>
       <c r="S932" s="16"/>
       <c r="T932" s="18" t="str">
-        <f>IF(C965&gt;18,IF(C965=20,_NW20,IF(C965=60,U934,IF(C965=50,_NW50,IF(C965=25,_NW25,IF(C965=32,_NW32,IF(C965=40,_NW40,"&gt;")))))),IF(C965=8,_NW8,IF(C965=6,_NW6,IF(C965=10,_NW10,IF(C965=18,_NW18,IF(C965=16,_NW16,IF(C965=12,_NW12,"")))))))</f>
+        <f>IF(C965&gt;18,IF(C965=20,Nennweite20,IF(C965=60,U934,IF(C965=50,Nennweite50,IF(C965=25,Nennweite25,IF(C965=32,Nennweite32,IF(C965=40,Nennweite40,"&gt;")))))),IF(C965=8,Nennweite8,IF(C965=6,Nennweite6,IF(C965=10,Nennweite10,IF(C965=18,Nennweite18,IF(C965=16,Nennweite16,IF(C965=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U932" s="16" t="s">
@@ -54195,7 +54195,7 @@
       </c>
       <c r="S962" s="16"/>
       <c r="T962" s="18" t="str">
-        <f>IF(C995&gt;18,IF(C995=20,_NW20,IF(C995=60,U964,IF(C995=50,_NW50,IF(C995=25,_NW25,IF(C995=32,_NW32,IF(C995=40,_NW40,"&gt;")))))),IF(C995=8,_NW8,IF(C995=6,_NW6,IF(C995=10,_NW10,IF(C995=18,_NW18,IF(C995=16,_NW16,IF(C995=12,_NW12,"")))))))</f>
+        <f>IF(C995&gt;18,IF(C995=20,Nennweite20,IF(C995=60,U964,IF(C995=50,Nennweite50,IF(C995=25,Nennweite25,IF(C995=32,Nennweite32,IF(C995=40,Nennweite40,"&gt;")))))),IF(C995=8,Nennweite8,IF(C995=6,Nennweite6,IF(C995=10,Nennweite10,IF(C995=18,Nennweite18,IF(C995=16,Nennweite16,IF(C995=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U962" s="16" t="s">
@@ -55629,7 +55629,7 @@
       </c>
       <c r="S992" s="16"/>
       <c r="T992" s="18" t="str">
-        <f>IF(C1025&gt;18,IF(C1025=20,_NW20,IF(C1025=60,U994,IF(C1025=50,_NW50,IF(C1025=25,_NW25,IF(C1025=32,_NW32,IF(C1025=40,_NW40,"&gt;")))))),IF(C1025=8,_NW8,IF(C1025=6,_NW6,IF(C1025=10,_NW10,IF(C1025=18,_NW18,IF(C1025=16,_NW16,IF(C1025=12,_NW12,"")))))))</f>
+        <f>IF(C1025&gt;18,IF(C1025=20,Nennweite20,IF(C1025=60,U994,IF(C1025=50,Nennweite50,IF(C1025=25,Nennweite25,IF(C1025=32,Nennweite32,IF(C1025=40,Nennweite40,"&gt;")))))),IF(C1025=8,Nennweite8,IF(C1025=6,Nennweite6,IF(C1025=10,Nennweite10,IF(C1025=18,Nennweite18,IF(C1025=16,Nennweite16,IF(C1025=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U992" s="16" t="s">
@@ -57063,7 +57063,7 @@
       </c>
       <c r="S1022" s="16"/>
       <c r="T1022" s="18" t="str">
-        <f>IF(C1055&gt;18,IF(C1055=20,_NW20,IF(C1055=60,U1024,IF(C1055=50,_NW50,IF(C1055=25,_NW25,IF(C1055=32,_NW32,IF(C1055=40,_NW40,"&gt;")))))),IF(C1055=8,_NW8,IF(C1055=6,_NW6,IF(C1055=10,_NW10,IF(C1055=18,_NW18,IF(C1055=16,_NW16,IF(C1055=12,_NW12,"")))))))</f>
+        <f>IF(C1055&gt;18,IF(C1055=20,Nennweite20,IF(C1055=60,U1024,IF(C1055=50,Nennweite50,IF(C1055=25,Nennweite25,IF(C1055=32,Nennweite32,IF(C1055=40,Nennweite40,"&gt;")))))),IF(C1055=8,Nennweite8,IF(C1055=6,Nennweite6,IF(C1055=10,Nennweite10,IF(C1055=18,Nennweite18,IF(C1055=16,Nennweite16,IF(C1055=12,Nennweite12,"")))))))</f>
         <v/>
       </c>
       <c r="U1022" s="16" t="s">
@@ -58393,7 +58393,7 @@
       <printOptions horizontalCentered="1"/>
       <pageSetup paperSize="9" scale="98" orientation="landscape" r:id="rId1"/>
       <headerFooter scaleWithDoc="0"/>
-      <autoFilter ref="B1:P1" xr:uid="{3E65EAEC-ED28-430D-8618-9EB13E287049}"/>
+      <autoFilter ref="B1:P1" xr:uid="{1063F259-8CDD-4BD1-845D-6B2B9DBB6254}"/>
       <extLst>
         <ext xmlns:xlsdti="http://schemas.microsoft.com/office/spreadsheetml/2023/showDataTypeIcons" uri="{a3c15fd4-4149-4032-8f15-062bd4999b60}">
           <xlsdti:showDataTypeIconsCustomSheetView visible="0"/>
@@ -60413,42 +60413,42 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="14">
-    <dataValidation type="list" allowBlank="1" sqref="B125:B144 B1025:B1044 B7:B24 B35:B54 B65:B84 B95:B114 B155:B174 B185:B204 B215:B234 B245:B264 B275:B294 B305:B324 B335:B354 B365:B384 B395:B414 B425:B444 B455:B474 B485:B504 B515:B534 B545:B564 B575:B594 B605:B624 B635:B654 B665:B684 B695:B714 B725:B744 B755:B774 B785:B804 B815:B834 B845:B864 B875:B894 B905:B924 B935:B954 B965:B984 B995:B1014 B5" xr:uid="{7B3CF2A4-E466-4DA6-95C9-9C0AE98110A2}">
+    <dataValidation type="list" allowBlank="1" sqref="B125:B144 B1025:B1044 B7:B24 B35:B54 B65:B84 B95:B114 B155:B174 B185:B204 B215:B234 B245:B264 B275:B294 B305:B324 B335:B354 B365:B384 B395:B414 B425:B444 B455:B474 B485:B504 B515:B534 B545:B564 B575:B594 B605:B624 B635:B654 B665:B684 B695:B714 B725:B744 B755:B774 B785:B804 B815:B834 B845:B864 B875:B894 B905:B924 B935:B954 B965:B984 B995:B1014 B5" xr:uid="{2A94878A-E30E-4611-BB3B-F98811E22990}">
       <formula1>Schlauch</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D35:D54 D65:D84 D365:D384 D335:D354 D95:D114 D125:D144 D155:D174 D185:D204 D215:D234 D245:D264 D275:D294 D305:D324 D5:D24 D395:D414 D425:D444 D725:D744 D695:D714 D455:D474 D485:D504 D515:D534 D545:D564 D575:D594 D605:D624 D635:D654 D665:D684 D755:D774 D785:D804 D815:D834 D845:D864 D875:D894 D905:D924 D935:D954 D965:D984 D995:D1014 D1025:D1044" xr:uid="{1329BC97-3D03-4104-94F8-7A2706BD2579}">
-      <formula1>IF(C5&gt;18,IF(C5=20,NW20,IF(C5=60,NW60,IF(C5=50,NW50,IF(C5=25,NW25,IF(C5=32,NW32,IF(C5=40,NW40,"&gt;")))))),IF(C5=8,NW8,IF(C5=6,NW6,IF(C5=10,NW10,IF(C5=18,NW18,IF(C5=16,NW16,IF(C5=12,NW12,"")))))))</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D35:D54 D65:D84 D365:D384 D335:D354 D95:D114 D125:D144 D155:D174 D185:D204 D215:D234 D245:D264 D275:D294 D305:D324 D5:D24 D395:D414 D425:D444 D725:D744 D695:D714 D455:D474 D485:D504 D515:D534 D545:D564 D575:D594 D605:D624 D635:D654 D665:D684 D755:D774 D785:D804 D815:D834 D845:D864 D875:D894 D905:D924 D935:D954 D965:D984 D995:D1014 D1025:D1044" xr:uid="{09505AAE-EFA6-4889-B010-E3B934A7A625}">
+      <formula1>IF(C5&gt;18,IF(C5=20,Nennweite20,IF(C5=60,Nennweite60,IF(C5=50,Nennweite50,IF(C5=25,Nennweite25,IF(C5=32,Nennweite32,IF(C5=40,Nennweite40,"&gt;")))))),IF(C5=8,Nennweite8,IF(C5=6,Nennweite6,IF(C5=10,Nennweite10,IF(C5=18,Nennweite18,IF(C5=16,Nennweite16,IF(C5=12,Nennweite12,"")))))))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E65:E84 E335:E354 E365:E384 E35:E54 E95:E114 E125:E144 E155:E174 E185:E204 E215:E234 E245:E264 E275:E294 E305:E324 E5:E24 E425:E444 E695:E714 E725:E744 E395:E414 E455:E474 E485:E504 E515:E534 E545:E564 E575:E594 E605:E624 E635:E654 E665:E684 E755:E774 E785:E804 E815:E834 E845:E864 E875:E894 E905:E924 E935:E954 E965:E984 E995:E1014 E1025:E1044" xr:uid="{DE6CDD7D-9D51-4EE0-88B8-979F297898D1}">
-      <formula1>IF(C5&gt;18,IF(C5=20,NW20,IF(C5=60,NW60,IF(C5=50,NW50,IF(C5=25,NW25,IF(C5=32,NW32,IF(C5=40,NW40,"&gt;")))))),IF(C5=8,NW8,IF(C5=6,NW6,IF(C5=10,NW10,IF(C5=18,NW18,IF(C5=16,NW16,IF(C5=12,NW12,"")))))))</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E65:E84 E335:E354 E365:E384 E35:E54 E95:E114 E125:E144 E155:E174 E185:E204 E215:E234 E245:E264 E275:E294 E305:E324 E5:E24 E425:E444 E695:E714 E725:E744 E395:E414 E455:E474 E485:E504 E515:E534 E545:E564 E575:E594 E605:E624 E635:E654 E665:E684 E755:E774 E785:E804 E815:E834 E845:E864 E875:E894 E905:E924 E935:E954 E965:E984 E995:E1014 E1025:E1044" xr:uid="{28869F7F-ECBD-4C37-847C-9377DFD1CF1A}">
+      <formula1>IF(C5&gt;18,IF(C5=20,Nennweite20,IF(C5=60,Nennweite60,IF(C5=50,Nennweite50,IF(C5=25,Nennweite25,IF(C5=32,Nennweite32,IF(C5=40,Nennweite40,"&gt;")))))),IF(C5=8,Nennweite8,IF(C5=6,Nennweite6,IF(C5=10,Nennweite10,IF(C5=18,Nennweite18,IF(C5=16,Nennweite16,IF(C5=12,Nennweite12,"")))))))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5:H24 G65:H84 G365:H384 G335:H354 G95:H114 G125:H144 G155:H174 G185:H204 G215:H234 G245:H264 G275:H294 G305:H324 G35:H54 G425:H444 G725:H744 G695:H714 G455:H474 G485:H504 G515:H534 G545:H564 G575:H594 G605:H624 G635:H654 G665:H684 G395:H414 G755:H774 G785:H804 G815:H834 G845:H864 G875:H894 G905:H924 G935:H954 G965:H984 G995:H1014 G1025:H1044" xr:uid="{8250C9A5-E4E3-4ECD-96F8-C6D89D598715}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5:H24 G65:H84 G365:H384 G335:H354 G95:H114 G125:H144 G155:H174 G185:H204 G215:H234 G245:H264 G275:H294 G305:H324 G35:H54 G425:H444 G725:H744 G695:H714 G455:H474 G485:H504 G515:H534 G545:H564 G575:H594 G605:H624 G635:H654 G665:H684 G395:H414 G755:H774 G785:H804 G815:H834 G845:H864 G875:H894 G905:H924 G935:H954 G965:H984 G995:H1014 G1025:H1044" xr:uid="{7EACE20F-B3D5-4AA0-8EED-A48790384EE7}">
       <formula1>"0,45,90,135,180,215,270,315"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K65:K84 K365:K384 K335:K354 K5:K24 K95:K114 K125:K144 K155:K174 K185:K204 K215:K234 K245:K264 K275:K294 K305:K324 K35:K54 K425:K444 K725:K744 K695:K714 K455:K474 K485:K504 K515:K534 K545:K564 K575:K594 K605:K624 K635:K654 K665:K684 K395:K414 K755:K774 K785:K804 K815:K834 K845:K864 K875:K894 K905:K924 K935:K954 K965:K984 K995:K1014 K1025:K1044" xr:uid="{1F5E9AA4-2F48-4C89-9B9A-78DC48E8E5D1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K65:K84 K365:K384 K335:K354 K5:K24 K95:K114 K125:K144 K155:K174 K185:K204 K215:K234 K245:K264 K275:K294 K305:K324 K35:K54 K425:K444 K725:K744 K695:K714 K455:K474 K485:K504 K515:K534 K545:K564 K575:K594 K605:K624 K635:K654 K665:K684 K395:K414 K755:K774 K785:K804 K815:K834 K845:K864 K875:K894 K905:K924 K935:K954 K965:K984 K995:K1014 K1025:K1044" xr:uid="{84F4FA5C-289B-4273-A667-D594A5B5F2D2}">
       <formula1>"1,2,3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="C696:C697" xr:uid="{B41A62C8-B1C5-455C-AC62-4BF3CBFE2A6A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="C696:C697" xr:uid="{324524FE-FEDB-4F5C-8910-ACAC7C9FF5BF}">
       <formula1>"6,8,10,12,16,20,25,32,40,50,60,"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" sqref="I182:I184 I332:I334 I2:I4 I272:I274 I122:I124 I152:I154 I302:I304 I572:I574 I32:I34 I62:I64 I242:I244 I92:I94 I212:I214 I722:I724 I542:I544 I692:I694 I632:I634 I482:I484 I512:I514 I662:I664 I362:I364 I392:I394 I422:I424 I602:I604 I452:I454 I752:I754 I782:I784 I812:I814 I842:I844 I872:I874 I902:I904 I932:I934 I962:I964 I992:I994 I1051:I65536 I1022:I1024" xr:uid="{377215A1-2686-438F-B64C-89908CEB9EFE}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I114 I369" xr:uid="{B245BC06-247F-429F-AB7D-A72F24394EAE}">
+    <dataValidation allowBlank="1" showInputMessage="1" sqref="I182:I184 I332:I334 I2:I4 I272:I274 I122:I124 I152:I154 I302:I304 I572:I574 I32:I34 I62:I64 I242:I244 I92:I94 I212:I214 I722:I724 I542:I544 I692:I694 I632:I634 I482:I484 I512:I514 I662:I664 I362:I364 I392:I394 I422:I424 I602:I604 I452:I454 I752:I754 I782:I784 I812:I814 I842:I844 I872:I874 I902:I904 I932:I934 I962:I964 I992:I994 I1051:I65536 I1022:I1024" xr:uid="{F570D8B0-3A63-4C74-85D2-E2C4D3748317}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I114 I369" xr:uid="{182CD363-9DDA-4835-9F15-E7C9D377F32F}">
       <formula1>"450,425,420,415,400,380,350,330,320,310,290,280,275,250,225,215,210,180,165,160,130,125,105,90,88,80,50,40"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C5:C24 C35:C54 C65:C84 C95:C114 C125:C144 C155:C174 C185:C204 C215:C234 C245:C264 C275:C294 C305:C324 C335:C354 C365:C384 C395:C414 C425:C444 C455:C474 C485:C504 C515:C534 C545:C564 C575:C594 C605:C624 C635:C654 C665:C684 C695 C698:C714 C725:C744 C755:C774 C785:C804 C815:C834 C845:C864 C875:C894 C905:C924 C935:C954 C965:C984 C995:C1014 C1025:C1044" xr:uid="{F12334CD-F622-4E01-B9EA-84D7564919EC}">
+    <dataValidation type="list" allowBlank="1" sqref="C5:C24 C35:C54 C65:C84 C95:C114 C125:C144 C155:C174 C185:C204 C215:C234 C245:C264 C275:C294 C305:C324 C335:C354 C365:C384 C395:C414 C425:C444 C455:C474 C485:C504 C515:C534 C545:C564 C575:C594 C605:C624 C635:C654 C665:C684 C695 C698:C714 C725:C744 C755:C774 C785:C804 C815:C834 C845:C864 C875:C894 C905:C924 C935:C954 C965:C984 C995:C1014 C1025:C1044" xr:uid="{5BF60EE6-906E-4DDE-8122-7CB6A4B7B72B}">
       <formula1>"2,4,6,8,10,12,16,20,25,32,40,50,60,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I24 I35:I54 I65:I84 I95:I113 I125:I144 I155:I174 I185:I204 I215:I234 I245:I264 I275:I294 I305:I324 I335:I354 I365:I368 I370:I384 I395:I414 I425:I444 I455:I474 I485:I504 I515:I534 I545:I564 I575:I594 I605:I624 I635:I654 I665:I684 I695:I714 I725:I744 I755:I774 I785:I804 I815:I834 I845:I864 I875:I894 I905:I924 I935:I954 I965:I984 I995:I1014 I1025:I1044" xr:uid="{75318DAC-3448-4035-AC75-BBBD12032D5B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I24 I35:I54 I65:I84 I95:I113 I125:I144 I155:I174 I185:I204 I215:I234 I245:I264 I275:I294 I305:I324 I335:I354 I365:I368 I370:I384 I395:I414 I425:I444 I455:I474 I485:I504 I515:I534 I545:I564 I575:I594 I605:I624 I635:I654 I665:I684 I695:I714 I725:I744 I755:I774 I785:I804 I815:I834 I845:I864 I875:I894 I905:I924 I935:I954 I965:I984 I995:I1014 I1025:I1044" xr:uid="{8E393546-38C5-41BE-A363-A9674FD8B147}">
       <formula1>"700,630,450,425,420,415,400,380,350,330,320,315,310,290,280,275,250,225,215,210,180,165,160,130,125,105,90,88,80,50,40,10,7"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" sqref="B6" xr:uid="{098AAED5-6953-4EE8-B469-922336B81F06}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L995:L1014 L5:L24 L335:L354 L35:L54 L65:L84 L95:L114 L125:L144 L155:L174 L185:L204 L215:L234 L245:L264 L275:L294 L305:L324 L365:L384 L395:L414 L425:L444 L455:L474 L485:L504 L515:L534 L545:L564 L575:L594 L605:L624 L635:L654 L665:L684 L695:L714 L725:L744 L755:L774 L785:L804 L815:L834 L845:L864 L875:L894 L905:L924 L935:L954 L965:L984 L1025:L1044" xr:uid="{EEDED31F-DE45-4203-83D7-3E115168322B}">
+    <dataValidation allowBlank="1" sqref="B6" xr:uid="{85E51C37-E5D8-41C9-BB61-4F216BAFDA43}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L995:L1014 L5:L24 L335:L354 L35:L54 L65:L84 L95:L114 L125:L144 L155:L174 L185:L204 L215:L234 L245:L264 L275:L294 L305:L324 L365:L384 L395:L414 L425:L444 L455:L474 L485:L504 L515:L534 L545:L564 L575:L594 L605:L624 L635:L654 L665:L684 L695:L714 L725:L744 L755:L774 L785:L804 L815:L834 L845:L864 L875:L894 L905:L924 L935:L954 L965:L984 L1025:L1044" xr:uid="{C27A5BFB-2D80-44D0-B87E-FEE42C27FADE}">
       <formula1>"12,24,48,60,72"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N5:N24 N65:N68 N95:N98 N125:N128 N155:N158 N185:N188 N215:N218 N245:N248 N275:N278 N305:N308 N335:N338 N365:N368 N395:N414 N425:N444 N455:N474 N485:N504 N515:N534 N545:N564 N575:N594 N605:N624 N635:N654 N665:N684 N695:N714 N725:N744 N755:N774 N785:N804 N815:N834 N845:N864 N875:N894 N905:N924 N935:N954 N965:N984 N995:N1014 N1025:N1044" xr:uid="{E568913C-4865-4F81-8F2F-AC4504EA6EAB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N5:N24 N65:N68 N95:N98 N125:N128 N155:N158 N185:N188 N215:N218 N245:N248 N275:N278 N305:N308 N335:N338 N365:N368 N395:N414 N425:N444 N455:N474 N485:N504 N515:N534 N545:N564 N575:N594 N605:N624 N635:N654 N665:N684 N695:N714 N725:N744 N755:N774 N785:N804 N815:N834 N845:N864 N875:N894 N905:N924 N935:N954 N965:N984 N995:N1014 N1025:N1044" xr:uid="{674BDFE3-7662-4186-A281-BCBC04EB52C6}">
       <formula1>"OK, NOK"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N35:N54 N339:N358 N309:N328 N279:N298 N369:N388 N69:N85 N99:N116 N159:N178 N189:N208 N219:N238 N249:N268 N129:N147" xr:uid="{79A65DF9-0C64-4FEB-861C-1790E43FF52F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N35:N54 N339:N358 N309:N328 N279:N298 N369:N388 N69:N85 N99:N116 N159:N178 N189:N208 N219:N238 N249:N268 N129:N147" xr:uid="{CF4827A9-8694-4711-B1CA-6BEEE1CCE479}">
       <formula1>"OK,NOK,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -60497,7 +60497,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C522755-67F0-41F0-B0A0-69F16A0A1076}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3A7C0A5-101C-4BEF-8456-1D5EC6C43BF5}">
   <dimension ref="A1:C75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>

--- a/templates/XLSX-Muster.xlsx
+++ b/templates/XLSX-Muster.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m3-jo\OneDrive\Dokumente\Schlauchmanegtment App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D61B17A2-8B46-4B2A-A4E8-3D4C5D609E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31317CD9-C703-43CF-8DFF-DC5A3E8E302C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72EE3D34-AC63-438F-B259-F2BDB8CEDC4B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{72EE3D34-AC63-438F-B259-F2BDB8CEDC4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Auswahlseite" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1525,4 +1526,13 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B69737BA-265D-47EC-AF65-0D56774ECB8F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/templates/XLSX-Muster.xlsx
+++ b/templates/XLSX-Muster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m3-jo\OneDrive\Dokumente\Schlauchmanegtment App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31317CD9-C703-43CF-8DFF-DC5A3E8E302C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A06474-498F-424C-9D15-56AD49567811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{72EE3D34-AC63-438F-B259-F2BDB8CEDC4B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72EE3D34-AC63-438F-B259-F2BDB8CEDC4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -42,9 +42,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
-    <t xml:space="preserve">                                      Schlauchmanagement in Anlehnung an DGUV 113-020</t>
-  </si>
-  <si>
     <t>Betreiber</t>
   </si>
   <si>
@@ -148,6 +145,9 @@
   </si>
   <si>
     <t>Hydraulikschlauch, Gefährdung von Menschen bei Versagen möglich, Schutzmaßnahmen müssen vorhanden sein.</t>
+  </si>
+  <si>
+    <t>Schlauchmanagement in Anlehnung an DGUV 113-020</t>
   </si>
 </sst>
 </file>
@@ -342,9 +342,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -419,6 +416,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="7"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -435,6 +435,62 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>36708</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>962</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Grafik 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8160EC50-A20C-AC3F-8170-CB016E18F8DE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="-7461" r="-7461"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2772000" cy="612000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -769,726 +825,726 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="P2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q2" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="9" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+    </row>
+    <row r="4" spans="1:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
+      <c r="R4" s="29"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A5" s="25">
+        <v>1</v>
+      </c>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="26"/>
+      <c r="P5" s="26"/>
+      <c r="Q5" s="27"/>
+      <c r="R5" s="27"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A6" s="11">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A7" s="11">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A8" s="11">
+        <v>4</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A9" s="11">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A10" s="11">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A11" s="11">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A12" s="11">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A13" s="11">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A14" s="11">
+        <v>10</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A15" s="11">
+        <v>11</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A16" s="11">
+        <v>12</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A17" s="11">
+        <v>13</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A18" s="11">
+        <v>14</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A19" s="11">
+        <v>15</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A20" s="11">
+        <v>16</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="8"/>
+      <c r="R20" s="8"/>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A21" s="11">
+        <v>17</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6"/>
+      <c r="Q21" s="8"/>
+      <c r="R21" s="8"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A22" s="11">
+        <v>18</v>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="8"/>
+      <c r="R22" s="8"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A23" s="11">
+        <v>19</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="8"/>
+      <c r="R23" s="8"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A24" s="11">
+        <v>20</v>
+      </c>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="6"/>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="8"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A25" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="P2" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q2" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="R2" s="10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A3" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
-      <c r="R3" s="11"/>
-    </row>
-    <row r="4" spans="1:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A5" s="26">
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="20"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A26" s="8">
         <v>1</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="27"/>
-      <c r="M5" s="27"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="27"/>
-      <c r="P5" s="27"/>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" s="12">
+      <c r="B26" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13"/>
+      <c r="P26" s="13"/>
+      <c r="Q26" s="13"/>
+      <c r="R26" s="14"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="9"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A7" s="12">
+      <c r="B27" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13"/>
+      <c r="P27" s="13"/>
+      <c r="Q27" s="13"/>
+      <c r="R27" s="14"/>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A28" s="8">
         <v>3</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="9"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A8" s="12">
-        <v>4</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="9"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A9" s="12">
-        <v>5</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="9"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A10" s="12">
-        <v>6</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="9"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A11" s="12">
-        <v>7</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="9"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A12" s="12">
-        <v>8</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="9"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A13" s="12">
-        <v>9</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="9"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A14" s="12">
-        <v>10</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="9"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A15" s="12">
-        <v>11</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="9"/>
-      <c r="R15" s="9"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A16" s="12">
-        <v>12</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="9"/>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A17" s="12">
-        <v>13</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="9"/>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A18" s="12">
-        <v>14</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="9"/>
-      <c r="R18" s="9"/>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A19" s="12">
-        <v>15</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="9"/>
-      <c r="R19" s="9"/>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A20" s="12">
-        <v>16</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="9"/>
-      <c r="R20" s="9"/>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A21" s="12">
-        <v>17</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="9"/>
-      <c r="R21" s="9"/>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A22" s="12">
-        <v>18</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="9"/>
-      <c r="R22" s="9"/>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A23" s="12">
-        <v>19</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="9"/>
-      <c r="R23" s="9"/>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A24" s="12">
-        <v>20</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="9"/>
-      <c r="R24" s="9"/>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A25" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="19" t="s">
+      <c r="B28" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="13"/>
+      <c r="Q28" s="13"/>
+      <c r="R28" s="14"/>
+    </row>
+    <row r="29" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20"/>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
-      <c r="R25" s="21"/>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A26" s="9">
-        <v>1</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="14"/>
-      <c r="P26" s="14"/>
-      <c r="Q26" s="14"/>
-      <c r="R26" s="15"/>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A27" s="9">
-        <v>2</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="14"/>
-      <c r="O27" s="14"/>
-      <c r="P27" s="14"/>
-      <c r="Q27" s="14"/>
-      <c r="R27" s="15"/>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A28" s="9">
-        <v>3</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="14"/>
-      <c r="O28" s="14"/>
-      <c r="P28" s="14"/>
-      <c r="Q28" s="14"/>
-      <c r="R28" s="15"/>
-    </row>
-    <row r="29" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="s">
+      <c r="B29" s="22"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="F29" s="22"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="23"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="L29" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="M29" s="23"/>
+      <c r="N29" s="23"/>
+      <c r="O29" s="23"/>
+      <c r="P29" s="23"/>
+      <c r="Q29" s="23"/>
+      <c r="R29" s="22"/>
+    </row>
+    <row r="30" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B29" s="23"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="22" t="s">
+      <c r="B30" s="22"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F29" s="23"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="23"/>
-      <c r="K29" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="L29" s="22" t="s">
+      <c r="F30" s="22"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="23"/>
+      <c r="I30" s="23"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="M29" s="24"/>
-      <c r="N29" s="24"/>
-      <c r="O29" s="24"/>
-      <c r="P29" s="24"/>
-      <c r="Q29" s="24"/>
-      <c r="R29" s="23"/>
-    </row>
-    <row r="30" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" s="23"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="22" t="s">
+      <c r="L30" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="F30" s="23"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="24"/>
-      <c r="I30" s="24"/>
-      <c r="J30" s="23"/>
-      <c r="K30" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="L30" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="M30" s="24"/>
-      <c r="N30" s="24"/>
-      <c r="O30" s="24"/>
-      <c r="P30" s="24"/>
-      <c r="Q30" s="24"/>
-      <c r="R30" s="23"/>
+      <c r="M30" s="23"/>
+      <c r="N30" s="23"/>
+      <c r="O30" s="23"/>
+      <c r="P30" s="23"/>
+      <c r="Q30" s="23"/>
+      <c r="R30" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="31">
@@ -1525,6 +1581,7 @@
     <mergeCell ref="L2:L4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/templates/XLSX-Muster.xlsx
+++ b/templates/XLSX-Muster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m3-jo\OneDrive\Dokumente\Schlauchmanegtment App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A06474-498F-424C-9D15-56AD49567811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07607C03-31E5-44EF-B9E4-FDEDB43436DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72EE3D34-AC63-438F-B259-F2BDB8CEDC4B}"/>
   </bookViews>
@@ -39,8 +39,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
   <si>
     <t>Betreiber</t>
   </si>
@@ -145,9 +167,6 @@
   </si>
   <si>
     <t>Hydraulikschlauch, Gefährdung von Menschen bei Versagen möglich, Schutzmaßnahmen müssen vorhanden sein.</t>
-  </si>
-  <si>
-    <t>Schlauchmanagement in Anlehnung an DGUV 113-020</t>
   </si>
 </sst>
 </file>
@@ -437,60 +456,68 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>36708</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>962</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Grafik 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8160EC50-A20C-AC3F-8170-CB016E18F8DE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect l="-7461" r="-7461"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2772000" cy="612000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -825,8 +852,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
-        <v>35</v>
+      <c r="A1" s="30" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -1581,7 +1608,6 @@
     <mergeCell ref="L2:L4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/templates/XLSX-Muster.xlsx
+++ b/templates/XLSX-Muster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m3-jo\OneDrive\Dokumente\Schlauchmanegtment App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07607C03-31E5-44EF-B9E4-FDEDB43436DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE1D3887-E486-408A-BA20-7FC431201A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72EE3D34-AC63-438F-B259-F2BDB8CEDC4B}"/>
   </bookViews>
@@ -94,9 +94,6 @@
     <t>Anschluß B</t>
   </si>
   <si>
-    <t>Länge</t>
-  </si>
-  <si>
     <t>Lage A</t>
   </si>
   <si>
@@ -133,9 +130,6 @@
     <t>Bemerkung</t>
   </si>
   <si>
-    <t>Version: 1.1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Klassifizierung sicherheitstechnische Bewertung:                                                                     </t>
   </si>
   <si>
@@ -167,6 +161,12 @@
   </si>
   <si>
     <t>Hydraulikschlauch, Gefährdung von Menschen bei Versagen möglich, Schutzmaßnahmen müssen vorhanden sein.</t>
+  </si>
+  <si>
+    <t>Version: 2</t>
+  </si>
+  <si>
+    <t>V2</t>
   </si>
 </sst>
 </file>
@@ -887,46 +887,46 @@
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
       <c r="E2" s="8" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F2" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="H2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="I2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="J2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="K2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="L2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="M2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="N2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="O2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="9" t="s">
+      <c r="P2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="Q2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="R2" s="9" t="s">
         <v>21</v>
-      </c>
-      <c r="R2" s="9" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
@@ -1423,14 +1423,14 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" s="15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
       <c r="D25" s="16"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G25" s="19"/>
       <c r="H25" s="19"/>
@@ -1450,7 +1450,7 @@
         <v>1</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
@@ -1474,7 +1474,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
@@ -1498,7 +1498,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
@@ -1519,13 +1519,13 @@
     </row>
     <row r="29" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B29" s="22"/>
       <c r="C29" s="21"/>
       <c r="D29" s="22"/>
       <c r="E29" s="21" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F29" s="22"/>
       <c r="G29" s="21"/>
@@ -1533,10 +1533,10 @@
       <c r="I29" s="23"/>
       <c r="J29" s="22"/>
       <c r="K29" s="24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L29" s="21" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M29" s="23"/>
       <c r="N29" s="23"/>
@@ -1547,13 +1547,13 @@
     </row>
     <row r="30" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="21" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B30" s="22"/>
       <c r="C30" s="21"/>
       <c r="D30" s="22"/>
       <c r="E30" s="21" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F30" s="22"/>
       <c r="G30" s="21"/>
@@ -1561,10 +1561,10 @@
       <c r="I30" s="23"/>
       <c r="J30" s="22"/>
       <c r="K30" s="24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L30" s="21" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M30" s="23"/>
       <c r="N30" s="23"/>

--- a/templates/XLSX-Muster.xlsx
+++ b/templates/XLSX-Muster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m3-jo\OneDrive\Dokumente\Schlauchmanegtment App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE1D3887-E486-408A-BA20-7FC431201A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725434F5-FF6D-4E63-9DCC-64A7C11115F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72EE3D34-AC63-438F-B259-F2BDB8CEDC4B}"/>
   </bookViews>
@@ -39,30 +39,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
   <si>
     <t>Betreiber</t>
   </si>
@@ -133,9 +111,6 @@
     <t xml:space="preserve">Klassifizierung sicherheitstechnische Bewertung:                                                                     </t>
   </si>
   <si>
-    <t xml:space="preserve"> * Dokumentation des Ist-Zustands am Tag der Prüfung</t>
-  </si>
-  <si>
     <t>Ersteller:</t>
   </si>
   <si>
@@ -167,6 +142,15 @@
   </si>
   <si>
     <t>V2</t>
+  </si>
+  <si>
+    <t>v2</t>
+  </si>
+  <si>
+    <t>cdsaa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * Dokumentation des Ist-Zustands am Tag der Prüfungsssssssssssssss</t>
   </si>
 </sst>
 </file>
@@ -454,70 +438,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -843,7 +763,9 @@
     <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
     <col min="2" max="8" width="11.42578125" style="1"/>
     <col min="9" max="9" width="7.42578125" style="1" customWidth="1"/>
-    <col min="10" max="13" width="11.42578125" style="1"/>
+    <col min="10" max="10" width="11.42578125" style="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" customWidth="1"/>
+    <col min="12" max="13" width="11.42578125" style="1"/>
     <col min="14" max="14" width="11.42578125" style="2"/>
     <col min="15" max="16" width="11.42578125" style="1"/>
     <col min="17" max="17" width="11.42578125" style="2"/>
@@ -852,9 +774,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="A1" s="30"/>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
       <c r="D1" s="30"/>
@@ -887,10 +807,10 @@
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
       <c r="E2" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>33</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>34</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>10</v>
@@ -1055,7 +975,9 @@
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
+      <c r="F8" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -1430,7 +1352,7 @@
       <c r="D25" s="16"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G25" s="19"/>
       <c r="H25" s="19"/>
@@ -1450,7 +1372,7 @@
         <v>1</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
@@ -1474,7 +1396,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
@@ -1498,7 +1420,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
@@ -1519,13 +1441,13 @@
     </row>
     <row r="29" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B29" s="22"/>
       <c r="C29" s="21"/>
       <c r="D29" s="22"/>
       <c r="E29" s="21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F29" s="22"/>
       <c r="G29" s="21"/>
@@ -1533,10 +1455,10 @@
       <c r="I29" s="23"/>
       <c r="J29" s="22"/>
       <c r="K29" s="24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L29" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M29" s="23"/>
       <c r="N29" s="23"/>
@@ -1547,24 +1469,26 @@
     </row>
     <row r="30" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B30" s="22"/>
       <c r="C30" s="21"/>
       <c r="D30" s="22"/>
       <c r="E30" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F30" s="22"/>
-      <c r="G30" s="21"/>
+      <c r="G30" s="21" t="s">
+        <v>35</v>
+      </c>
       <c r="H30" s="23"/>
       <c r="I30" s="23"/>
       <c r="J30" s="22"/>
       <c r="K30" s="24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L30" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M30" s="23"/>
       <c r="N30" s="23"/>

--- a/templates/XLSX-Muster.xlsx
+++ b/templates/XLSX-Muster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m3-jo\OneDrive\Dokumente\Schlauchmanegtment App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725434F5-FF6D-4E63-9DCC-64A7C11115F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5936F41F-3D03-4135-BEC1-18D8AEE7BBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72EE3D34-AC63-438F-B259-F2BDB8CEDC4B}"/>
   </bookViews>
@@ -40,7 +40,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+  <si>
+    <t xml:space="preserve">                                      Schlauchmanagement in Anlehnung an DGUV 113-020</t>
+  </si>
   <si>
     <t>Betreiber</t>
   </si>
@@ -139,9 +142,6 @@
   </si>
   <si>
     <t>Version: 2</t>
-  </si>
-  <si>
-    <t>V2</t>
   </si>
   <si>
     <t>v2</t>
@@ -421,7 +421,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="7"/>
+      <alignment horizontal="right" vertical="center" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -438,6 +438,62 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>554539</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>3329</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Grafik 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4C44F0D-5465-4C02-304B-21A117A57AD2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="-3100" t="9524" r="-3100" b="9524"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="3286588" cy="612000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -774,7 +830,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30"/>
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
       <c r="D1" s="30"/>
@@ -786,72 +844,72 @@
       <c r="J1" s="30"/>
       <c r="K1" s="30"/>
       <c r="L1" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1" s="4"/>
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
       <c r="Q1" s="5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
       <c r="E2" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -873,19 +931,19 @@
     </row>
     <row r="4" spans="1:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" s="29"/>
       <c r="G4" s="29"/>
@@ -1345,7 +1403,7 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -1372,7 +1430,7 @@
         <v>1</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
@@ -1396,7 +1454,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
@@ -1420,7 +1478,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
@@ -1441,13 +1499,13 @@
     </row>
     <row r="29" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B29" s="22"/>
       <c r="C29" s="21"/>
       <c r="D29" s="22"/>
       <c r="E29" s="21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F29" s="22"/>
       <c r="G29" s="21"/>
@@ -1455,10 +1513,10 @@
       <c r="I29" s="23"/>
       <c r="J29" s="22"/>
       <c r="K29" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="L29" s="21" t="s">
         <v>28</v>
-      </c>
-      <c r="L29" s="21" t="s">
-        <v>27</v>
       </c>
       <c r="M29" s="23"/>
       <c r="N29" s="23"/>
@@ -1469,13 +1527,13 @@
     </row>
     <row r="30" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B30" s="22"/>
       <c r="C30" s="21"/>
       <c r="D30" s="22"/>
       <c r="E30" s="21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F30" s="22"/>
       <c r="G30" s="21" t="s">
@@ -1485,10 +1543,10 @@
       <c r="I30" s="23"/>
       <c r="J30" s="22"/>
       <c r="K30" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="L30" s="21" t="s">
         <v>28</v>
-      </c>
-      <c r="L30" s="21" t="s">
-        <v>27</v>
       </c>
       <c r="M30" s="23"/>
       <c r="N30" s="23"/>
@@ -1532,6 +1590,7 @@
     <mergeCell ref="L2:L4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/templates/XLSX-Muster.xlsx
+++ b/templates/XLSX-Muster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m3-jo\OneDrive\Dokumente\Schlauchmanegtment App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5936F41F-3D03-4135-BEC1-18D8AEE7BBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD6C80C-2CAD-439A-B460-F79649A49728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72EE3D34-AC63-438F-B259-F2BDB8CEDC4B}"/>
   </bookViews>
@@ -42,9 +42,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
   <si>
-    <t xml:space="preserve">                                      Schlauchmanagement in Anlehnung an DGUV 113-020</t>
-  </si>
-  <si>
     <t>Betreiber</t>
   </si>
   <si>
@@ -151,6 +148,9 @@
   </si>
   <si>
     <t xml:space="preserve"> * Dokumentation des Ist-Zustands am Tag der Prüfungsssssssssssssss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                      Schlauchmanagement in Anlehnung an DGUV 113-020XX</t>
   </si>
 </sst>
 </file>
@@ -831,7 +831,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="30" t="s">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -844,72 +844,72 @@
       <c r="J1" s="30"/>
       <c r="K1" s="30"/>
       <c r="L1" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1" s="4"/>
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
       <c r="Q1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="R1" s="5" t="s">
         <v>2</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
       <c r="E2" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="9" t="s">
+      <c r="I2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="J2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="K2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="L2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="M2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="N2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="O2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="9" t="s">
+      <c r="P2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="Q2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="R2" s="9" t="s">
         <v>21</v>
-      </c>
-      <c r="R2" s="9" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -931,19 +931,19 @@
     </row>
     <row r="4" spans="1:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="C4" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="D4" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="E4" s="28" t="s">
         <v>9</v>
-      </c>
-      <c r="E4" s="28" t="s">
-        <v>10</v>
       </c>
       <c r="F4" s="29"/>
       <c r="G4" s="29"/>
@@ -1034,7 +1034,7 @@
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
@@ -1403,14 +1403,14 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
       <c r="D25" s="16"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G25" s="19"/>
       <c r="H25" s="19"/>
@@ -1430,7 +1430,7 @@
         <v>1</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
@@ -1454,7 +1454,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
@@ -1478,7 +1478,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
@@ -1499,13 +1499,13 @@
     </row>
     <row r="29" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B29" s="22"/>
       <c r="C29" s="21"/>
       <c r="D29" s="22"/>
       <c r="E29" s="21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F29" s="22"/>
       <c r="G29" s="21"/>
@@ -1513,10 +1513,10 @@
       <c r="I29" s="23"/>
       <c r="J29" s="22"/>
       <c r="K29" s="24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L29" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M29" s="23"/>
       <c r="N29" s="23"/>
@@ -1527,26 +1527,26 @@
     </row>
     <row r="30" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B30" s="22"/>
       <c r="C30" s="21"/>
       <c r="D30" s="22"/>
       <c r="E30" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F30" s="22"/>
       <c r="G30" s="21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H30" s="23"/>
       <c r="I30" s="23"/>
       <c r="J30" s="22"/>
       <c r="K30" s="24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L30" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M30" s="23"/>
       <c r="N30" s="23"/>

--- a/templates/XLSX-Muster.xlsx
+++ b/templates/XLSX-Muster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m3-jo\OneDrive\Dokumente\Schlauchmanegtment App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD6C80C-2CAD-439A-B460-F79649A49728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046C87DF-02F0-44E1-8379-09C66CB9D2A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72EE3D34-AC63-438F-B259-F2BDB8CEDC4B}"/>
   </bookViews>
@@ -141,9 +141,6 @@
     <t>Version: 2</t>
   </si>
   <si>
-    <t>v2</t>
-  </si>
-  <si>
     <t>cdsaa</t>
   </si>
   <si>
@@ -151,6 +148,9 @@
   </si>
   <si>
     <t xml:space="preserve">                                      Schlauchmanagement in Anlehnung an DGUV 113-020XX</t>
+  </si>
+  <si>
+    <t>mit Bild und XX</t>
   </si>
 </sst>
 </file>
@@ -831,7 +831,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -1034,7 +1034,7 @@
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
@@ -1410,7 +1410,7 @@
       <c r="D25" s="16"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G25" s="19"/>
       <c r="H25" s="19"/>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="F30" s="22"/>
       <c r="G30" s="21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H30" s="23"/>
       <c r="I30" s="23"/>

--- a/templates/XLSX-Muster.xlsx
+++ b/templates/XLSX-Muster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m3-jo\OneDrive\Dokumente\Schlauchmanegtment App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046C87DF-02F0-44E1-8379-09C66CB9D2A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF7FF827-C9E9-4AF6-9209-7625F300A7EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72EE3D34-AC63-438F-B259-F2BDB8CEDC4B}"/>
   </bookViews>
@@ -39,8 +39,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
   <si>
     <t>Betreiber</t>
   </si>
@@ -147,10 +169,13 @@
     <t xml:space="preserve"> * Dokumentation des Ist-Zustands am Tag der Prüfungsssssssssssssss</t>
   </si>
   <si>
-    <t xml:space="preserve">                                      Schlauchmanagement in Anlehnung an DGUV 113-020XX</t>
-  </si>
-  <si>
-    <t>mit Bild und XX</t>
+    <t>Bild in Zelle</t>
+  </si>
+  <si>
+    <t>Bild über Zelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                      Schlauchmanagement in Anlehnung an DGUV 113-020</t>
   </si>
 </sst>
 </file>
@@ -348,63 +373,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -417,11 +391,62 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -442,25 +467,25 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>554539</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>3329</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>8423</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>94185</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Grafik 8">
+        <xdr:cNvPr id="2" name="Grafik 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4C44F0D-5465-4C02-304B-21A117A57AD2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DEB80CC-5685-0E28-9C17-8CC2922D1E4C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -468,23 +493,16 @@
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect l="-3100" t="9524" r="-3100" b="9524"/>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="3286588" cy="612000"/>
+          <a:off x="2732942" y="1905000"/>
+          <a:ext cx="2294423" cy="577762"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -494,6 +512,70 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -830,576 +912,580 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="P2" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q2" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="R2" s="24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
+    </row>
+    <row r="4" spans="1:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
+      <c r="R4" s="26"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A5" s="8">
+        <v>1</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A6" s="6">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A7" s="6">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" s="9" t="s">
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A9" s="6">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A12" s="6">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A13" s="6">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A14" s="6">
         <v>10</v>
       </c>
-      <c r="G2" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="9" t="s">
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A15" s="6">
         <v>11</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A16" s="6">
         <v>12</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A17" s="6">
         <v>13</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="5"/>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A18" s="6">
         <v>14</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A19" s="6">
         <v>15</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A20" s="6">
         <v>16</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="5"/>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A21" s="6">
         <v>17</v>
       </c>
-      <c r="O2" s="9" t="s">
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A22" s="6">
         <v>18</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A23" s="6">
         <v>19</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="5"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A24" s="6">
         <v>20</v>
       </c>
-      <c r="R2" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-    </row>
-    <row r="4" spans="1:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="29"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A5" s="25">
-        <v>1</v>
-      </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="27"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="26"/>
-      <c r="Q5" s="27"/>
-      <c r="R5" s="27"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" s="11">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A7" s="11">
-        <v>3</v>
-      </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A8" s="11">
-        <v>4</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A9" s="11">
-        <v>5</v>
-      </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A10" s="11">
-        <v>6</v>
-      </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A11" s="11">
-        <v>7</v>
-      </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A12" s="11">
-        <v>8</v>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A13" s="11">
-        <v>9</v>
-      </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A14" s="11">
-        <v>10</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A15" s="11">
-        <v>11</v>
-      </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A16" s="11">
-        <v>12</v>
-      </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A17" s="11">
-        <v>13</v>
-      </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A18" s="11">
-        <v>14</v>
-      </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A19" s="11">
-        <v>15</v>
-      </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="8"/>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A20" s="11">
-        <v>16</v>
-      </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-      <c r="Q20" s="8"/>
-      <c r="R20" s="8"/>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A21" s="11">
-        <v>17</v>
-      </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
-      <c r="Q21" s="8"/>
-      <c r="R21" s="8"/>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A22" s="11">
-        <v>18</v>
-      </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="8"/>
-      <c r="R22" s="8"/>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A23" s="11">
-        <v>19</v>
-      </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="8"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-      <c r="Q23" s="8"/>
-      <c r="R23" s="8"/>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A24" s="11">
-        <v>20</v>
-      </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" s="15" t="s">
@@ -1426,157 +1512,137 @@
       <c r="R25" s="20"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A26" s="8">
+      <c r="A26" s="5">
         <v>1</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="13"/>
-      <c r="N26" s="13"/>
-      <c r="O26" s="13"/>
-      <c r="P26" s="13"/>
-      <c r="Q26" s="13"/>
-      <c r="R26" s="14"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22"/>
+      <c r="R26" s="23"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A27" s="8">
+      <c r="A27" s="5">
         <v>2</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="13"/>
-      <c r="M27" s="13"/>
-      <c r="N27" s="13"/>
-      <c r="O27" s="13"/>
-      <c r="P27" s="13"/>
-      <c r="Q27" s="13"/>
-      <c r="R27" s="14"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22"/>
+      <c r="R27" s="23"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A28" s="8">
+      <c r="A28" s="5">
         <v>3</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
-      <c r="L28" s="13"/>
-      <c r="M28" s="13"/>
-      <c r="N28" s="13"/>
-      <c r="O28" s="13"/>
-      <c r="P28" s="13"/>
-      <c r="Q28" s="13"/>
-      <c r="R28" s="14"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22"/>
+      <c r="R28" s="23"/>
     </row>
     <row r="29" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="21" t="s">
+      <c r="B29" s="14"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F29" s="22"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="24" t="s">
+      <c r="F29" s="14"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="L29" s="21" t="s">
+      <c r="L29" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="M29" s="23"/>
-      <c r="N29" s="23"/>
-      <c r="O29" s="23"/>
-      <c r="P29" s="23"/>
-      <c r="Q29" s="23"/>
-      <c r="R29" s="22"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13"/>
+      <c r="P29" s="13"/>
+      <c r="Q29" s="13"/>
+      <c r="R29" s="14"/>
     </row>
     <row r="30" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="22"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="21" t="s">
+      <c r="B30" s="14"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="F30" s="22"/>
-      <c r="G30" s="21" t="s">
+      <c r="F30" s="14"/>
+      <c r="G30" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H30" s="23"/>
-      <c r="I30" s="23"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="24" t="s">
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="L30" s="21" t="s">
+      <c r="L30" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="M30" s="23"/>
-      <c r="N30" s="23"/>
-      <c r="O30" s="23"/>
-      <c r="P30" s="23"/>
-      <c r="Q30" s="23"/>
-      <c r="R30" s="22"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13"/>
+      <c r="P30" s="13"/>
+      <c r="Q30" s="13"/>
+      <c r="R30" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="L30:R30"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="G30:J30"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="F25:R25"/>
-    <mergeCell ref="B26:R26"/>
-    <mergeCell ref="B27:R27"/>
-    <mergeCell ref="B28:R28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="L29:R29"/>
-    <mergeCell ref="M2:M4"/>
-    <mergeCell ref="N2:N4"/>
-    <mergeCell ref="O2:O4"/>
-    <mergeCell ref="P2:P4"/>
-    <mergeCell ref="Q2:Q4"/>
     <mergeCell ref="R2:R4"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="L1:P1"/>
@@ -1588,6 +1654,26 @@
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="K2:K4"/>
     <mergeCell ref="L2:L4"/>
+    <mergeCell ref="M2:M4"/>
+    <mergeCell ref="N2:N4"/>
+    <mergeCell ref="O2:O4"/>
+    <mergeCell ref="P2:P4"/>
+    <mergeCell ref="Q2:Q4"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="F25:R25"/>
+    <mergeCell ref="B26:R26"/>
+    <mergeCell ref="B27:R27"/>
+    <mergeCell ref="B28:R28"/>
+    <mergeCell ref="L30:R30"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="L29:R29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/templates/XLSX-Muster.xlsx
+++ b/templates/XLSX-Muster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m3-jo\OneDrive\Dokumente\Schlauchmanegtment App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF7FF827-C9E9-4AF6-9209-7625F300A7EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EDFF806-6C49-4C83-89EB-B904EE2C5D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72EE3D34-AC63-438F-B259-F2BDB8CEDC4B}"/>
   </bookViews>
@@ -39,30 +39,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
   <si>
     <t>Betreiber</t>
   </si>
@@ -169,13 +147,10 @@
     <t xml:space="preserve"> * Dokumentation des Ist-Zustands am Tag der Prüfungsssssssssssssss</t>
   </si>
   <si>
-    <t>Bild in Zelle</t>
-  </si>
-  <si>
-    <t>Bild über Zelle</t>
-  </si>
-  <si>
     <t xml:space="preserve">                                      Schlauchmanagement in Anlehnung an DGUV 113-020</t>
+  </si>
+  <si>
+    <t>Bild über Zelle A1</t>
   </si>
 </sst>
 </file>
@@ -391,6 +366,54 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -398,54 +421,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -469,16 +444,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>8423</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>94185</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>487585</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1534</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -493,16 +468,17 @@
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill>
+      <xdr:blipFill rotWithShape="1">
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect l="-23203" t="7500" r="-43436" b="7500"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2732942" y="1905000"/>
-          <a:ext cx="2294423" cy="577762"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="4743528" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -512,70 +488,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -912,26 +824,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="28" t="s">
+      <c r="A1" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
       <c r="Q1" s="3" t="s">
         <v>1</v>
       </c>
@@ -943,49 +855,49 @@
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
       <c r="E2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="F2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="G2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="24" t="s">
+      <c r="H2" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="I2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="24" t="s">
+      <c r="J2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="24" t="s">
+      <c r="K2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="24" t="s">
+      <c r="L2" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="24" t="s">
+      <c r="M2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="24" t="s">
+      <c r="N2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="24" t="s">
+      <c r="O2" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="24" t="s">
+      <c r="P2" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" s="24" t="s">
+      <c r="Q2" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="R2" s="24" t="s">
+      <c r="R2" s="12" t="s">
         <v>21</v>
       </c>
     </row>
@@ -997,19 +909,19 @@
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
     </row>
     <row r="4" spans="1:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
@@ -1027,19 +939,19 @@
       <c r="E4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="26"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
@@ -1111,15 +1023,13 @@
       <c r="A8" s="6">
         <v>4</v>
       </c>
-      <c r="B8" s="4"/>
+      <c r="B8" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="4" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>35</v>
-      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
@@ -1187,9 +1097,7 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
-      <c r="H11" s="4" t="s">
-        <v>36</v>
-      </c>
+      <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -1488,161 +1396,176 @@
       <c r="R24" s="5"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="18" t="s">
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
-      <c r="R25" s="20"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="23"/>
+      <c r="N25" s="23"/>
+      <c r="O25" s="23"/>
+      <c r="P25" s="23"/>
+      <c r="Q25" s="23"/>
+      <c r="R25" s="24"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <v>1</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
-      <c r="M26" s="22"/>
-      <c r="N26" s="22"/>
-      <c r="O26" s="22"/>
-      <c r="P26" s="22"/>
-      <c r="Q26" s="22"/>
-      <c r="R26" s="23"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="26"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="26"/>
+      <c r="Q26" s="26"/>
+      <c r="R26" s="27"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>2</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="22"/>
-      <c r="M27" s="22"/>
-      <c r="N27" s="22"/>
-      <c r="O27" s="22"/>
-      <c r="P27" s="22"/>
-      <c r="Q27" s="22"/>
-      <c r="R27" s="23"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="26"/>
+      <c r="O27" s="26"/>
+      <c r="P27" s="26"/>
+      <c r="Q27" s="26"/>
+      <c r="R27" s="27"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>3</v>
       </c>
-      <c r="B28" s="21" t="s">
+      <c r="B28" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="22"/>
-      <c r="N28" s="22"/>
-      <c r="O28" s="22"/>
-      <c r="P28" s="22"/>
-      <c r="Q28" s="22"/>
-      <c r="R28" s="23"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="26"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="26"/>
+      <c r="Q28" s="26"/>
+      <c r="R28" s="27"/>
     </row>
     <row r="29" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B29" s="14"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="12" t="s">
+      <c r="B29" s="30"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="F29" s="14"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="14"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="30"/>
       <c r="K29" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="L29" s="12" t="s">
+      <c r="L29" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="13"/>
-      <c r="P29" s="13"/>
-      <c r="Q29" s="13"/>
-      <c r="R29" s="14"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="29"/>
+      <c r="R29" s="30"/>
     </row>
     <row r="30" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="12" t="s">
+      <c r="B30" s="30"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="F30" s="14"/>
-      <c r="G30" s="12" t="s">
+      <c r="F30" s="30"/>
+      <c r="G30" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="14"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="30"/>
       <c r="K30" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="L30" s="12" t="s">
+      <c r="L30" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="M30" s="13"/>
-      <c r="N30" s="13"/>
-      <c r="O30" s="13"/>
-      <c r="P30" s="13"/>
-      <c r="Q30" s="13"/>
-      <c r="R30" s="14"/>
+      <c r="M30" s="29"/>
+      <c r="N30" s="29"/>
+      <c r="O30" s="29"/>
+      <c r="P30" s="29"/>
+      <c r="Q30" s="29"/>
+      <c r="R30" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="L30:R30"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="L29:R29"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="F25:R25"/>
+    <mergeCell ref="B26:R26"/>
+    <mergeCell ref="B27:R27"/>
+    <mergeCell ref="B28:R28"/>
     <mergeCell ref="R2:R4"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="L1:P1"/>
@@ -1659,21 +1582,6 @@
     <mergeCell ref="O2:O4"/>
     <mergeCell ref="P2:P4"/>
     <mergeCell ref="Q2:Q4"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="F25:R25"/>
-    <mergeCell ref="B26:R26"/>
-    <mergeCell ref="B27:R27"/>
-    <mergeCell ref="B28:R28"/>
-    <mergeCell ref="L30:R30"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="G30:J30"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="L29:R29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/templates/XLSX-Muster.xlsx
+++ b/templates/XLSX-Muster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m3-jo\OneDrive\Dokumente\Schlauchmanegtment App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EDFF806-6C49-4C83-89EB-B904EE2C5D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D50F62DC-A3E8-4C82-AB7E-9712183A59F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72EE3D34-AC63-438F-B259-F2BDB8CEDC4B}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="50">
   <si>
     <t>Betreiber</t>
   </si>
@@ -150,7 +150,46 @@
     <t xml:space="preserve">                                      Schlauchmanagement in Anlehnung an DGUV 113-020</t>
   </si>
   <si>
-    <t>Bild über Zelle A1</t>
+    <t>1SN</t>
+  </si>
+  <si>
+    <t>2SN</t>
+  </si>
+  <si>
+    <t>4SP</t>
+  </si>
+  <si>
+    <t>4SH</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>R15</t>
+  </si>
+  <si>
+    <t>1TE</t>
+  </si>
+  <si>
+    <t>2TE</t>
+  </si>
+  <si>
+    <t>3TE</t>
+  </si>
+  <si>
+    <t>Minimess</t>
+  </si>
+  <si>
+    <t>Teflon</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>2245N</t>
+  </si>
+  <si>
+    <t>Mit DropDown</t>
   </si>
 </sst>
 </file>
@@ -339,7 +378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -421,6 +460,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1023,9 +1065,7 @@
       <c r="A8" s="6">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>36</v>
-      </c>
+      <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -1070,7 +1110,9 @@
         <v>6</v>
       </c>
       <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
+      <c r="C10" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -1585,14 +1627,97 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{81CCD811-A5A8-42CC-9AAC-C114820FAF0A}">
+          <x14:formula1>
+            <xm:f>Auswahlseite!$A$1:$A$14</xm:f>
+          </x14:formula1>
+          <xm:sqref>B5:B24</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B69737BA-265D-47EC-AF65-0D56774ECB8F}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="31" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="31" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="31" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="31" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="31">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="31" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="31" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="31" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="31" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="31" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/templates/XLSX-Muster.xlsx
+++ b/templates/XLSX-Muster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m3-jo\OneDrive\Dokumente\Schlauchmanegtment App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D50F62DC-A3E8-4C82-AB7E-9712183A59F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C71B5733-27A4-417B-B44F-FC8CAF4E44AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72EE3D34-AC63-438F-B259-F2BDB8CEDC4B}"/>
   </bookViews>
@@ -405,6 +405,45 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -424,45 +463,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -866,26 +866,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="16" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
       <c r="Q1" s="3" t="s">
         <v>1</v>
       </c>
@@ -897,49 +897,49 @@
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
       <c r="E2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="12" t="s">
+      <c r="N2" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="12" t="s">
+      <c r="O2" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="12" t="s">
+      <c r="P2" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="Q2" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="R2" s="12" t="s">
+      <c r="R2" s="25" t="s">
         <v>21</v>
       </c>
     </row>
@@ -951,19 +951,19 @@
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
     </row>
     <row r="4" spans="1:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
@@ -981,19 +981,19 @@
       <c r="E4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
@@ -1438,176 +1438,162 @@
       <c r="R24" s="5"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="22" t="s">
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="23"/>
-      <c r="M25" s="23"/>
-      <c r="N25" s="23"/>
-      <c r="O25" s="23"/>
-      <c r="P25" s="23"/>
-      <c r="Q25" s="23"/>
-      <c r="R25" s="24"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
+      <c r="R25" s="21"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <v>1</v>
       </c>
-      <c r="B26" s="25" t="s">
+      <c r="B26" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
-      <c r="K26" s="26"/>
-      <c r="L26" s="26"/>
-      <c r="M26" s="26"/>
-      <c r="N26" s="26"/>
-      <c r="O26" s="26"/>
-      <c r="P26" s="26"/>
-      <c r="Q26" s="26"/>
-      <c r="R26" s="27"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="23"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="23"/>
+      <c r="L26" s="23"/>
+      <c r="M26" s="23"/>
+      <c r="N26" s="23"/>
+      <c r="O26" s="23"/>
+      <c r="P26" s="23"/>
+      <c r="Q26" s="23"/>
+      <c r="R26" s="24"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>2</v>
       </c>
-      <c r="B27" s="25" t="s">
+      <c r="B27" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-      <c r="K27" s="26"/>
-      <c r="L27" s="26"/>
-      <c r="M27" s="26"/>
-      <c r="N27" s="26"/>
-      <c r="O27" s="26"/>
-      <c r="P27" s="26"/>
-      <c r="Q27" s="26"/>
-      <c r="R27" s="27"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
+      <c r="I27" s="23"/>
+      <c r="J27" s="23"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="23"/>
+      <c r="M27" s="23"/>
+      <c r="N27" s="23"/>
+      <c r="O27" s="23"/>
+      <c r="P27" s="23"/>
+      <c r="Q27" s="23"/>
+      <c r="R27" s="24"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>3</v>
       </c>
-      <c r="B28" s="25" t="s">
+      <c r="B28" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-      <c r="K28" s="26"/>
-      <c r="L28" s="26"/>
-      <c r="M28" s="26"/>
-      <c r="N28" s="26"/>
-      <c r="O28" s="26"/>
-      <c r="P28" s="26"/>
-      <c r="Q28" s="26"/>
-      <c r="R28" s="27"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="23"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="23"/>
+      <c r="Q28" s="23"/>
+      <c r="R28" s="24"/>
     </row>
     <row r="29" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="28" t="s">
+      <c r="B29" s="15"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F29" s="30"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="30"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="15"/>
       <c r="K29" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="L29" s="28" t="s">
+      <c r="L29" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="M29" s="29"/>
-      <c r="N29" s="29"/>
-      <c r="O29" s="29"/>
-      <c r="P29" s="29"/>
-      <c r="Q29" s="29"/>
-      <c r="R29" s="30"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
+      <c r="O29" s="14"/>
+      <c r="P29" s="14"/>
+      <c r="Q29" s="14"/>
+      <c r="R29" s="15"/>
     </row>
     <row r="30" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="30"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="28" t="s">
+      <c r="B30" s="15"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="F30" s="30"/>
-      <c r="G30" s="28" t="s">
+      <c r="F30" s="15"/>
+      <c r="G30" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="30"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="15"/>
       <c r="K30" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="L30" s="28" t="s">
+      <c r="L30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="M30" s="29"/>
-      <c r="N30" s="29"/>
-      <c r="O30" s="29"/>
-      <c r="P30" s="29"/>
-      <c r="Q30" s="29"/>
-      <c r="R30" s="30"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
+      <c r="O30" s="14"/>
+      <c r="P30" s="14"/>
+      <c r="Q30" s="14"/>
+      <c r="R30" s="15"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="6K1x6nXQbjmQmESNcxTdDbuDLAfDORmGskrgUFNM63fDwULyuROKsGJ6/HX0wbebCku0zbuBNhcMdaKAaJtEcg==" saltValue="J+X8TGJGAs4oNdGQaXyzGw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="31">
-    <mergeCell ref="L30:R30"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="G30:J30"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="L29:R29"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="F25:R25"/>
-    <mergeCell ref="B26:R26"/>
-    <mergeCell ref="B27:R27"/>
-    <mergeCell ref="B28:R28"/>
     <mergeCell ref="R2:R4"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="L1:P1"/>
@@ -1624,6 +1610,21 @@
     <mergeCell ref="O2:O4"/>
     <mergeCell ref="P2:P4"/>
     <mergeCell ref="Q2:Q4"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="F25:R25"/>
+    <mergeCell ref="B26:R26"/>
+    <mergeCell ref="B27:R27"/>
+    <mergeCell ref="B28:R28"/>
+    <mergeCell ref="L30:R30"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="L29:R29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1648,72 +1649,72 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="12" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="12" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="12" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="12" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="31">
+      <c r="A7" s="12">
         <v>462</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="12" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="12" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="12" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="12" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="12" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="12" t="s">
         <v>48</v>
       </c>
     </row>

--- a/templates/XLSX-Muster.xlsx
+++ b/templates/XLSX-Muster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m3-jo\OneDrive\Dokumente\Schlauchmanegtment App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C71B5733-27A4-417B-B44F-FC8CAF4E44AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E6A1E91-98DE-42AC-A1BC-22B9110851D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72EE3D34-AC63-438F-B259-F2BDB8CEDC4B}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
   <si>
     <t>Betreiber</t>
   </si>
@@ -190,6 +190,9 @@
   </si>
   <si>
     <t>Mit DropDown</t>
+  </si>
+  <si>
+    <t>Ohne Blattschutz</t>
   </si>
 </sst>
 </file>
@@ -1134,7 +1137,9 @@
         <v>7</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
+      <c r="C11" s="4" t="s">
+        <v>50</v>
+      </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
@@ -1592,7 +1597,6 @@
       <c r="R30" s="15"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="6K1x6nXQbjmQmESNcxTdDbuDLAfDORmGskrgUFNM63fDwULyuROKsGJ6/HX0wbebCku0zbuBNhcMdaKAaJtEcg==" saltValue="J+X8TGJGAs4oNdGQaXyzGw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="31">
     <mergeCell ref="R2:R4"/>
     <mergeCell ref="A1:K1"/>

--- a/templates/XLSX-Muster.xlsx
+++ b/templates/XLSX-Muster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m3-jo\OneDrive\Dokumente\Schlauchmanegtment App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E6A1E91-98DE-42AC-A1BC-22B9110851D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C42C0F4-09F4-48A5-A41D-2FA9187BA189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72EE3D34-AC63-438F-B259-F2BDB8CEDC4B}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
     <sheet name="Auswahlseite" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="Schlauch">Auswahlseite!$A$1:$A$14</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -144,9 +147,6 @@
     <t>cdsaa</t>
   </si>
   <si>
-    <t xml:space="preserve"> * Dokumentation des Ist-Zustands am Tag der Prüfungsssssssssssssss</t>
-  </si>
-  <si>
     <t xml:space="preserve">                                      Schlauchmanagement in Anlehnung an DGUV 113-020</t>
   </si>
   <si>
@@ -193,6 +193,9 @@
   </si>
   <si>
     <t>Ohne Blattschutz</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> * Dokumentation des Ist-Zustands am Tag der Prüfung</t>
   </si>
 </sst>
 </file>
@@ -411,6 +414,54 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -418,54 +469,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -869,26 +872,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="29" t="s">
+      <c r="A1" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
       <c r="Q1" s="3" t="s">
         <v>1</v>
       </c>
@@ -900,49 +903,49 @@
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="25" t="s">
+      <c r="I2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="25" t="s">
+      <c r="J2" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="25" t="s">
+      <c r="K2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="25" t="s">
+      <c r="L2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="25" t="s">
+      <c r="M2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="25" t="s">
+      <c r="N2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="25" t="s">
+      <c r="O2" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="25" t="s">
+      <c r="P2" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" s="25" t="s">
+      <c r="Q2" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="R2" s="25" t="s">
+      <c r="R2" s="13" t="s">
         <v>21</v>
       </c>
     </row>
@@ -954,19 +957,19 @@
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
     </row>
     <row r="4" spans="1:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
@@ -984,19 +987,19 @@
       <c r="E4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="27"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="27"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
@@ -1114,7 +1117,7 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -1138,7 +1141,7 @@
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -1443,161 +1446,176 @@
       <c r="R24" s="5"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20"/>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
-      <c r="R25" s="21"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="24"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="24"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="25"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <v>1</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="23"/>
-      <c r="K26" s="23"/>
-      <c r="L26" s="23"/>
-      <c r="M26" s="23"/>
-      <c r="N26" s="23"/>
-      <c r="O26" s="23"/>
-      <c r="P26" s="23"/>
-      <c r="Q26" s="23"/>
-      <c r="R26" s="24"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="27"/>
+      <c r="K26" s="27"/>
+      <c r="L26" s="27"/>
+      <c r="M26" s="27"/>
+      <c r="N26" s="27"/>
+      <c r="O26" s="27"/>
+      <c r="P26" s="27"/>
+      <c r="Q26" s="27"/>
+      <c r="R26" s="28"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>2</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="23"/>
-      <c r="M27" s="23"/>
-      <c r="N27" s="23"/>
-      <c r="O27" s="23"/>
-      <c r="P27" s="23"/>
-      <c r="Q27" s="23"/>
-      <c r="R27" s="24"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27"/>
+      <c r="K27" s="27"/>
+      <c r="L27" s="27"/>
+      <c r="M27" s="27"/>
+      <c r="N27" s="27"/>
+      <c r="O27" s="27"/>
+      <c r="P27" s="27"/>
+      <c r="Q27" s="27"/>
+      <c r="R27" s="28"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>3</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="23"/>
-      <c r="O28" s="23"/>
-      <c r="P28" s="23"/>
-      <c r="Q28" s="23"/>
-      <c r="R28" s="24"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="27"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+      <c r="M28" s="27"/>
+      <c r="N28" s="27"/>
+      <c r="O28" s="27"/>
+      <c r="P28" s="27"/>
+      <c r="Q28" s="27"/>
+      <c r="R28" s="28"/>
     </row>
     <row r="29" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="13" t="s">
+      <c r="B29" s="31"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="F29" s="15"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="15"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="31"/>
       <c r="K29" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="L29" s="13" t="s">
+      <c r="L29" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="M29" s="14"/>
-      <c r="N29" s="14"/>
-      <c r="O29" s="14"/>
-      <c r="P29" s="14"/>
-      <c r="Q29" s="14"/>
-      <c r="R29" s="15"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="31"/>
     </row>
     <row r="30" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="13" t="s">
+      <c r="B30" s="31"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="F30" s="15"/>
-      <c r="G30" s="13" t="s">
+      <c r="F30" s="31"/>
+      <c r="G30" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="15"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="31"/>
       <c r="K30" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="L30" s="13" t="s">
+      <c r="L30" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="14"/>
-      <c r="P30" s="14"/>
-      <c r="Q30" s="14"/>
-      <c r="R30" s="15"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="30"/>
+      <c r="P30" s="30"/>
+      <c r="Q30" s="30"/>
+      <c r="R30" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="L30:R30"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="L29:R29"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="F25:R25"/>
+    <mergeCell ref="B26:R26"/>
+    <mergeCell ref="B27:R27"/>
+    <mergeCell ref="B28:R28"/>
     <mergeCell ref="R2:R4"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="L1:P1"/>
@@ -1614,36 +1632,14 @@
     <mergeCell ref="O2:O4"/>
     <mergeCell ref="P2:P4"/>
     <mergeCell ref="Q2:Q4"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="F25:R25"/>
-    <mergeCell ref="B26:R26"/>
-    <mergeCell ref="B27:R27"/>
-    <mergeCell ref="B28:R28"/>
-    <mergeCell ref="L30:R30"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="G30:J30"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="L29:R29"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5:B24" xr:uid="{81CCD811-A5A8-42CC-9AAC-C114820FAF0A}">
+      <formula1>Schlauch</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{81CCD811-A5A8-42CC-9AAC-C114820FAF0A}">
-          <x14:formula1>
-            <xm:f>Auswahlseite!$A$1:$A$14</xm:f>
-          </x14:formula1>
-          <xm:sqref>B5:B24</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -1654,32 +1650,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -1689,37 +1685,37 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
